--- a/data/Master Standardisation_SAF.xlsx
+++ b/data/Master Standardisation_SAF.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ethz-my.sharepoint.com/personal/ksievert_ethz_ch/Documents/SAF/SAF Paper_Katrin/Meta Analysis_SAF/Harmonization_SAF/Harmonization Sheets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yash/Documents/GitHub/DACCSvDACCU/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="400" documentId="13_ncr:1_{163BC89A-D6A2-0946-8BDF-FCD88C056711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{792F5B07-128A-4E3E-93E4-D9E1335CF8EF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11229852-6CE2-7D40-A6A1-059FB9802CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="10" xr2:uid="{FC0504A6-912F-4B1B-B557-65BC8E554F24}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" firstSheet="1" activeTab="2" xr2:uid="{FC0504A6-912F-4B1B-B557-65BC8E554F24}"/>
   </bookViews>
   <sheets>
     <sheet name="Intro" sheetId="1" r:id="rId1"/>
@@ -1531,16 +1531,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="171" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0.000_-;\-* #,##0.000_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="_(* #,##0.000_);_(* \(#,##0.000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="170" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2029,7 +2029,7 @@
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -2038,12 +2038,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2056,7 +2056,7 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2065,17 +2065,17 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2084,16 +2084,16 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="10" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="10" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="10" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2107,19 +2107,19 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="168" fontId="10" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="10" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="10" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="10" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2128,7 +2128,7 @@
     <xf numFmtId="1" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="4" applyFont="1"/>
@@ -2158,10 +2158,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="fill"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -4309,9 +4309,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8418090-0B0B-C248-B9C6-3EA8C5996CC0}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4324,9 +4324,9 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECD3D274-F87F-004D-AFCB-52C1DFF64CB5}">
   <dimension ref="A1:U32"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:21">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" t="str" cm="1">
         <f t="array" ref="A1:U32">TRANSPOSE('Study Parameters'!A2:AF22)</f>
         <v>Reference</v>
@@ -4392,7 +4392,7 @@
         <v>Peacock et. al.</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
         <v>Included?</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>Yes</v>
       </c>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
         <v>Year</v>
       </c>
@@ -4522,7 +4522,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
         <v>DOI</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>https://doi.org/10.1016/j.ijhydene.2023.09.094</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
         <v>Pathway</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>e-Fuels</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
         <v>Pathway Detail</v>
       </c>
@@ -4717,7 +4717,7 @@
         <v>Fischer Tropsch</v>
       </c>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
         <v>Timeline</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>2024-2050</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
         <v>Learning Rates</v>
       </c>
@@ -4847,7 +4847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
         <v>Cost Type</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>Production Cost</v>
       </c>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
         <v>Cost Range Short Term</v>
       </c>
@@ -4977,7 +4977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
         <v>Cost Range 2050</v>
       </c>
@@ -5042,7 +5042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
         <v>Unit</v>
       </c>
@@ -5107,7 +5107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:21">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
         <v>WACC / Discount Rate</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
         <v>Electricity Price Range (EUR/MWh)</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
         <v>Electricty Price Source</v>
       </c>
@@ -5302,7 +5302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:21">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
         <v>Battery Storage</v>
       </c>
@@ -5367,7 +5367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:21">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
         <v>H2/H2O Source</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>PEM, Solid Oxide</v>
       </c>
     </row>
-    <row r="18" spans="1:21">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
         <v>co-SOEC route?</v>
       </c>
@@ -5497,7 +5497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:21">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
         <v>Electrolyser Cost Range (EUR/kW)</v>
       </c>
@@ -5562,7 +5562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:21">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
         <v>H2 Price (EUR/kg)</v>
       </c>
@@ -5627,7 +5627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:21">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
         <v>H2 Price Source</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:21">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
         <v>H2 Storage</v>
       </c>
@@ -5758,7 +5758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:21">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
         <v>CO2 Price Range ($/tCO2)</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:21">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
         <v>CO2 Price Source</v>
       </c>
@@ -5889,7 +5889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:21">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
         <v>CO2 Storage</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:21">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
         <v>CO2 consumption (kg/kg fuel)</v>
       </c>
@@ -6019,7 +6019,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="27" spans="1:21">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
         <v>Fuel Emissions Intensity (gCO2/MJ)</v>
       </c>
@@ -6084,7 +6084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:21">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
         <v>Fossil Fuel Price (EUR/l)</v>
       </c>
@@ -6149,7 +6149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:21">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
         <v>Annual Production</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="30" spans="1:21">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
         <v>Unit</v>
       </c>
@@ -6279,7 +6279,7 @@
         <v>litres</v>
       </c>
     </row>
-    <row r="31" spans="1:21">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
         <v>Project Lifetime (Years)</v>
       </c>
@@ -6344,7 +6344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:21">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
         <v>LCA Methdology</v>
       </c>
@@ -6420,19 +6420,19 @@
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
   <dimension ref="A1:T51"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="19" width="18.25" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="19" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="15.6">
+    <row r="1" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -6491,7 +6491,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="15.6">
+    <row r="2" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>309</v>
       </c>
@@ -6547,7 +6547,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="15.6">
+    <row r="3" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>369</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="15.6">
+    <row r="4" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>326</v>
       </c>
@@ -6667,7 +6667,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="15.6">
+    <row r="5" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>326</v>
       </c>
@@ -6719,7 +6719,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="15.6">
+    <row r="6" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>323</v>
       </c>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="S6" s="13"/>
     </row>
-    <row r="7" spans="1:20" ht="15.6">
+    <row r="7" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>261</v>
       </c>
@@ -6838,7 +6838,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="15.6">
+    <row r="8" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>261</v>
       </c>
@@ -6891,7 +6891,7 @@
         <v>58035000</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="15.6">
+    <row r="9" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>261</v>
       </c>
@@ -6958,7 +6958,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="15.6">
+    <row r="10" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>339</v>
       </c>
@@ -7026,7 +7026,7 @@
         <v>39140033.75</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15.6">
+    <row r="11" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>339</v>
       </c>
@@ -7097,7 +7097,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="15.6">
+    <row r="12" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>380</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15.6">
+    <row r="13" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>380</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="15.6">
+    <row r="14" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>380</v>
       </c>
@@ -7266,7 +7266,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="15.6">
+    <row r="15" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>380</v>
       </c>
@@ -7317,7 +7317,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="15.6">
+    <row r="16" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>380</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="15.6">
+    <row r="17" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>380</v>
       </c>
@@ -7435,7 +7435,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="15.6">
+    <row r="18" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>380</v>
       </c>
@@ -7486,7 +7486,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="15.6">
+    <row r="19" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>380</v>
       </c>
@@ -7537,7 +7537,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="15.6">
+    <row r="20" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>380</v>
       </c>
@@ -7588,7 +7588,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="21" spans="1:20" ht="15.6">
+    <row r="21" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>380</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="22" spans="1:20" ht="15.6">
+    <row r="22" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>237</v>
       </c>
@@ -7695,7 +7695,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:20" ht="15.6">
+    <row r="23" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>237</v>
       </c>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="T23" s="20"/>
     </row>
-    <row r="24" spans="1:20" ht="15.6">
+    <row r="24" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>223</v>
       </c>
@@ -7805,7 +7805,7 @@
         <v>3650000</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="15.6">
+    <row r="25" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>281</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="15.6">
+    <row r="26" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>281</v>
       </c>
@@ -7944,7 +7944,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="15.6">
+    <row r="27" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>281</v>
       </c>
@@ -8000,7 +8000,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="15.6">
+    <row r="28" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>348</v>
       </c>
@@ -8053,7 +8053,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="16.899999999999999" customHeight="1">
+    <row r="29" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>348</v>
       </c>
@@ -8109,7 +8109,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="30" spans="1:20" ht="16.899999999999999" customHeight="1">
+    <row r="30" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>348</v>
       </c>
@@ -8162,7 +8162,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="31" spans="1:20" ht="15.6">
+    <row r="31" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>348</v>
       </c>
@@ -8227,7 +8227,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="15.6">
+    <row r="32" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>348</v>
       </c>
@@ -8280,7 +8280,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="33" spans="1:20" ht="15.6">
+    <row r="33" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>348</v>
       </c>
@@ -8345,7 +8345,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="34" spans="1:20" ht="15.6">
+    <row r="34" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>305</v>
       </c>
@@ -8413,7 +8413,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="35" spans="1:20" ht="15.6">
+    <row r="35" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>292</v>
       </c>
@@ -8481,7 +8481,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="36" spans="1:20" ht="15.6">
+    <row r="36" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>332</v>
       </c>
@@ -8549,7 +8549,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="37" spans="1:20" ht="15.6">
+    <row r="37" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>332</v>
       </c>
@@ -8614,7 +8614,7 @@
         <v>1250000000</v>
       </c>
     </row>
-    <row r="38" spans="1:20" ht="15.6">
+    <row r="38" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>250</v>
       </c>
@@ -8682,7 +8682,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="39" spans="1:20" ht="15.6">
+    <row r="39" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>250</v>
       </c>
@@ -8738,7 +8738,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:20" ht="15.6">
+    <row r="40" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>250</v>
       </c>
@@ -8794,7 +8794,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="41" spans="1:20" ht="15.6">
+    <row r="41" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>250</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="42" spans="1:20" ht="15.6">
+    <row r="42" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>250</v>
       </c>
@@ -8921,7 +8921,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="43" spans="1:20" ht="15.6">
+    <row r="43" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>250</v>
       </c>
@@ -8977,7 +8977,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="44" spans="1:20" ht="15.6">
+    <row r="44" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>202</v>
       </c>
@@ -9045,7 +9045,7 @@
         <v>2110761</v>
       </c>
     </row>
-    <row r="45" spans="1:20" ht="15.6">
+    <row r="45" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>202</v>
       </c>
@@ -9116,7 +9116,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="46" spans="1:20" ht="15.6">
+    <row r="46" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>315</v>
       </c>
@@ -9171,7 +9171,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:20" ht="15.6">
+    <row r="47" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>315</v>
       </c>
@@ -9226,7 +9226,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:20" ht="15.6">
+    <row r="48" spans="1:20" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>269</v>
       </c>
@@ -9273,14 +9273,14 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="8:12" ht="15.6">
+    <row r="49" spans="8:12" ht="16" x14ac:dyDescent="0.2">
       <c r="H49" s="75"/>
       <c r="I49" s="75"/>
       <c r="J49" s="75"/>
       <c r="K49" s="75"/>
       <c r="L49" s="75"/>
     </row>
-    <row r="51" spans="8:12" ht="15.6">
+    <row r="51" spans="8:12" ht="16" x14ac:dyDescent="0.2">
       <c r="H51" s="75"/>
       <c r="I51" s="75"/>
       <c r="K51" s="75"/>
@@ -9330,18 +9330,18 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BB431A-E662-5C41-9045-CF84C3CAD717}">
   <dimension ref="A1:W50"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="8" max="11" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.75" customWidth="1"/>
-    <col min="14" max="14" width="59.75" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.75" customWidth="1"/>
+    <col min="8" max="11" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="59.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.6640625" customWidth="1"/>
     <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="14.75" customWidth="1"/>
-    <col min="23" max="23" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.6640625" customWidth="1"/>
+    <col min="23" max="23" width="17.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -9409,7 +9409,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>315</v>
       </c>
@@ -9466,7 +9466,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>380</v>
       </c>
@@ -9519,7 +9519,7 @@
         <v>58035000</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>237</v>
       </c>
@@ -9577,7 +9577,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>261</v>
       </c>
@@ -9636,7 +9636,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>380</v>
       </c>
@@ -9701,7 +9701,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>380</v>
       </c>
@@ -9754,7 +9754,7 @@
         <v>58035000</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>309</v>
       </c>
@@ -9819,7 +9819,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>305</v>
       </c>
@@ -9892,7 +9892,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>202</v>
       </c>
@@ -9957,7 +9957,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>261</v>
       </c>
@@ -10027,7 +10027,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>281</v>
       </c>
@@ -10084,7 +10084,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>281</v>
       </c>
@@ -10157,7 +10157,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>281</v>
       </c>
@@ -10222,7 +10222,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>339</v>
       </c>
@@ -10290,7 +10290,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>323</v>
       </c>
@@ -10354,7 +10354,7 @@
         <v>39140033.75</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>237</v>
       </c>
@@ -10416,7 +10416,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>250</v>
       </c>
@@ -10478,7 +10478,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>250</v>
       </c>
@@ -10540,7 +10540,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>261</v>
       </c>
@@ -10602,7 +10602,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>315</v>
       </c>
@@ -10664,7 +10664,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>348</v>
       </c>
@@ -10720,7 +10720,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>250</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>250</v>
       </c>
@@ -10842,7 +10842,7 @@
         <v>2110761</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>380</v>
       </c>
@@ -10900,7 +10900,7 @@
         <v>1250000000</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>250</v>
       </c>
@@ -10973,7 +10973,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>348</v>
       </c>
@@ -11035,7 +11035,7 @@
         <v>144778221.668742</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>250</v>
       </c>
@@ -11092,7 +11092,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>223</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>39140033.75</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>380</v>
       </c>
@@ -11204,7 +11204,7 @@
         <v>45872966</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>202</v>
       </c>
@@ -11277,7 +11277,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>380</v>
       </c>
@@ -11335,7 +11335,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>292</v>
       </c>
@@ -11405,7 +11405,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>348</v>
       </c>
@@ -11459,7 +11459,7 @@
         <v>25105853.051058531</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>380</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>380</v>
       </c>
@@ -11584,7 +11584,7 @@
         <v>208032000</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>369</v>
       </c>
@@ -11654,7 +11654,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>348</v>
       </c>
@@ -11713,7 +11713,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>380</v>
       </c>
@@ -11771,7 +11771,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>339</v>
       </c>
@@ -11841,7 +11841,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="41" spans="1:23">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>380</v>
       </c>
@@ -11899,7 +11899,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="42" spans="1:23">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>348</v>
       </c>
@@ -11966,7 +11966,7 @@
         <v>3650000</v>
       </c>
     </row>
-    <row r="43" spans="1:23">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>348</v>
       </c>
@@ -12026,7 +12026,7 @@
       </c>
       <c r="W43" s="115"/>
     </row>
-    <row r="44" spans="1:23">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>332</v>
       </c>
@@ -12096,7 +12096,7 @@
         <v>1250000000</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>332</v>
       </c>
@@ -12169,7 +12169,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>269</v>
       </c>
@@ -12212,7 +12212,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>326</v>
       </c>
@@ -12248,13 +12248,13 @@
         <v>2110761</v>
       </c>
     </row>
-    <row r="49" spans="11:15">
+    <row r="49" spans="11:15" x14ac:dyDescent="0.2">
       <c r="K49">
         <f>AVERAGEIF(F:F,2050,K:K)</f>
         <v>1339.8346764756116</v>
       </c>
     </row>
-    <row r="50" spans="11:15">
+    <row r="50" spans="11:15" x14ac:dyDescent="0.2">
       <c r="O50" s="75"/>
     </row>
   </sheetData>
@@ -12272,9 +12272,9 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5589645-AC03-4DEF-BB9F-5B34F0CEDB41}">
   <dimension ref="A1:T48"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -12333,7 +12333,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>309</v>
       </c>
@@ -12385,7 +12385,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>369</v>
       </c>
@@ -12445,7 +12445,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>326</v>
       </c>
@@ -12493,7 +12493,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>326</v>
       </c>
@@ -12541,7 +12541,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>323</v>
       </c>
@@ -12596,7 +12596,7 @@
       </c>
       <c r="S6" s="13"/>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>261</v>
       </c>
@@ -12648,7 +12648,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>261</v>
       </c>
@@ -12697,7 +12697,7 @@
         <v>58035000</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>261</v>
       </c>
@@ -12756,7 +12756,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>339</v>
       </c>
@@ -12815,7 +12815,7 @@
         <v>39140033.75</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>339</v>
       </c>
@@ -12877,7 +12877,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>380</v>
       </c>
@@ -12924,7 +12924,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>380</v>
       </c>
@@ -12983,7 +12983,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>380</v>
       </c>
@@ -13030,7 +13030,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>380</v>
       </c>
@@ -13077,7 +13077,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>380</v>
       </c>
@@ -13124,7 +13124,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>380</v>
       </c>
@@ -13183,7 +13183,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>380</v>
       </c>
@@ -13230,7 +13230,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>380</v>
       </c>
@@ -13277,7 +13277,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>380</v>
       </c>
@@ -13324,7 +13324,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>380</v>
       </c>
@@ -13371,7 +13371,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>237</v>
       </c>
@@ -13422,7 +13422,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>237</v>
       </c>
@@ -13474,7 +13474,7 @@
       </c>
       <c r="T23" s="20"/>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>223</v>
       </c>
@@ -13523,7 +13523,7 @@
         <v>3650000</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>281</v>
       </c>
@@ -13585,7 +13585,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>281</v>
       </c>
@@ -13644,7 +13644,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>281</v>
       </c>
@@ -13695,7 +13695,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>348</v>
       </c>
@@ -13743,7 +13743,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>348</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>348</v>
       </c>
@@ -13842,7 +13842,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>348</v>
       </c>
@@ -13898,7 +13898,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>348</v>
       </c>
@@ -13946,7 +13946,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>348</v>
       </c>
@@ -14002,7 +14002,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>305</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>292</v>
       </c>
@@ -14122,7 +14122,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>332</v>
       </c>
@@ -14182,7 +14182,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>332</v>
       </c>
@@ -14239,7 +14239,7 @@
         <v>1250000000</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>250</v>
       </c>
@@ -14298,7 +14298,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>250</v>
       </c>
@@ -14349,7 +14349,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>250</v>
       </c>
@@ -14400,7 +14400,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="41" spans="1:20">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>250</v>
       </c>
@@ -14451,7 +14451,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>250</v>
       </c>
@@ -14513,7 +14513,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>250</v>
       </c>
@@ -14564,7 +14564,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>202</v>
       </c>
@@ -14623,7 +14623,7 @@
         <v>2110761</v>
       </c>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>202</v>
       </c>
@@ -14685,7 +14685,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>315</v>
       </c>
@@ -14736,7 +14736,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>315</v>
       </c>
@@ -14787,7 +14787,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>269</v>
       </c>
@@ -14840,9 +14840,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2144F8DC-159B-4F66-B175-7947C46506AD}">
   <dimension ref="A1:T48"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -14901,7 +14901,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>309</v>
       </c>
@@ -14948,7 +14948,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>369</v>
       </c>
@@ -15007,7 +15007,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>326</v>
       </c>
@@ -15051,7 +15051,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>326</v>
       </c>
@@ -15095,7 +15095,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>323</v>
       </c>
@@ -15148,7 +15148,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>261</v>
       </c>
@@ -15195,7 +15195,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>261</v>
       </c>
@@ -15239,7 +15239,7 @@
         <v>58035000</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>261</v>
       </c>
@@ -15298,7 +15298,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>339</v>
       </c>
@@ -15357,7 +15357,7 @@
         <v>39140033.75</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>339</v>
       </c>
@@ -15419,7 +15419,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>380</v>
       </c>
@@ -15466,7 +15466,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>380</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>380</v>
       </c>
@@ -15572,7 +15572,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>380</v>
       </c>
@@ -15619,7 +15619,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>380</v>
       </c>
@@ -15666,7 +15666,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>380</v>
       </c>
@@ -15725,7 +15725,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>380</v>
       </c>
@@ -15772,7 +15772,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>380</v>
       </c>
@@ -15819,7 +15819,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>380</v>
       </c>
@@ -15866,7 +15866,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>380</v>
       </c>
@@ -15913,7 +15913,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>237</v>
       </c>
@@ -15960,7 +15960,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>237</v>
       </c>
@@ -16007,7 +16007,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>223</v>
       </c>
@@ -16051,7 +16051,7 @@
         <v>3650000</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>281</v>
       </c>
@@ -16113,7 +16113,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>281</v>
       </c>
@@ -16172,7 +16172,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>281</v>
       </c>
@@ -16219,7 +16219,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>348</v>
       </c>
@@ -16263,7 +16263,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>348</v>
       </c>
@@ -16310,7 +16310,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>348</v>
       </c>
@@ -16354,7 +16354,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>348</v>
       </c>
@@ -16410,7 +16410,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>348</v>
       </c>
@@ -16454,7 +16454,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>348</v>
       </c>
@@ -16510,7 +16510,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>305</v>
       </c>
@@ -16569,7 +16569,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>292</v>
       </c>
@@ -16628,7 +16628,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>332</v>
       </c>
@@ -16687,7 +16687,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>332</v>
       </c>
@@ -16743,7 +16743,7 @@
         <v>1250000000</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>250</v>
       </c>
@@ -16802,7 +16802,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>250</v>
       </c>
@@ -16849,7 +16849,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>250</v>
       </c>
@@ -16896,7 +16896,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="41" spans="1:20">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>250</v>
       </c>
@@ -16943,7 +16943,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>250</v>
       </c>
@@ -17005,7 +17005,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>250</v>
       </c>
@@ -17052,7 +17052,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>202</v>
       </c>
@@ -17111,7 +17111,7 @@
         <v>2110761</v>
       </c>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>202</v>
       </c>
@@ -17173,7 +17173,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>315</v>
       </c>
@@ -17220,7 +17220,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>315</v>
       </c>
@@ -17267,7 +17267,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>269</v>
       </c>
@@ -17315,9 +17315,9 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{883C42CF-98A9-1F42-9B54-2E233A2C74A3}">
   <dimension ref="A1:S47"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -17373,7 +17373,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>281</v>
       </c>
@@ -17432,7 +17432,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>202</v>
       </c>
@@ -17488,7 +17488,7 @@
         <v>2110761</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>223</v>
       </c>
@@ -17533,7 +17533,7 @@
         <v>3650000</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>380</v>
       </c>
@@ -17577,7 +17577,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>380</v>
       </c>
@@ -17633,7 +17633,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>323</v>
       </c>
@@ -17683,7 +17683,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>250</v>
       </c>
@@ -17739,7 +17739,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>250</v>
       </c>
@@ -17787,7 +17787,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>250</v>
       </c>
@@ -17835,7 +17835,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>380</v>
       </c>
@@ -17879,7 +17879,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>315</v>
       </c>
@@ -17927,7 +17927,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>269</v>
       </c>
@@ -17961,7 +17961,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>369</v>
       </c>
@@ -18017,7 +18017,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>281</v>
       </c>
@@ -18073,7 +18073,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>281</v>
       </c>
@@ -18121,7 +18121,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>237</v>
       </c>
@@ -18169,7 +18169,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>250</v>
       </c>
@@ -18217,7 +18217,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>309</v>
       </c>
@@ -18268,7 +18268,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>237</v>
       </c>
@@ -18317,7 +18317,7 @@
       </c>
       <c r="S20" s="20"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>250</v>
       </c>
@@ -18376,7 +18376,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>250</v>
       </c>
@@ -18424,7 +18424,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>202</v>
       </c>
@@ -18483,7 +18483,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>339</v>
       </c>
@@ -18539,7 +18539,7 @@
         <v>39140033.75</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>315</v>
       </c>
@@ -18587,7 +18587,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>326</v>
       </c>
@@ -18614,7 +18614,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>380</v>
       </c>
@@ -18658,7 +18658,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>292</v>
       </c>
@@ -18714,7 +18714,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>380</v>
       </c>
@@ -18758,7 +18758,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>339</v>
       </c>
@@ -18817,7 +18817,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>305</v>
       </c>
@@ -18876,7 +18876,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>332</v>
       </c>
@@ -18935,7 +18935,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>348</v>
       </c>
@@ -18980,7 +18980,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>348</v>
       </c>
@@ -19028,7 +19028,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>348</v>
       </c>
@@ -19073,7 +19073,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>348</v>
       </c>
@@ -19126,7 +19126,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>348</v>
       </c>
@@ -19171,7 +19171,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>348</v>
       </c>
@@ -19224,7 +19224,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>261</v>
       </c>
@@ -19272,7 +19272,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>261</v>
       </c>
@@ -19317,7 +19317,7 @@
         <v>58035000</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>261</v>
       </c>
@@ -19373,7 +19373,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>332</v>
       </c>
@@ -19429,7 +19429,7 @@
         <v>1250000000</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>380</v>
       </c>
@@ -19485,7 +19485,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>380</v>
       </c>
@@ -19529,7 +19529,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>380</v>
       </c>
@@ -19573,7 +19573,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>380</v>
       </c>
@@ -19617,7 +19617,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>380</v>
       </c>
@@ -19672,9 +19672,9 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE362AFC-A479-4947-AC17-22830BE4F6C8}">
   <dimension ref="A1:S50"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="76" t="s">
         <v>4</v>
       </c>
@@ -19731,7 +19731,7 @@
       </c>
       <c r="S1" s="76"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="76" t="s">
         <v>281</v>
       </c>
@@ -19790,7 +19790,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="76" t="s">
         <v>202</v>
       </c>
@@ -19847,7 +19847,7 @@
       </c>
       <c r="S3" s="76"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="76" t="s">
         <v>223</v>
       </c>
@@ -19896,7 +19896,7 @@
       </c>
       <c r="S4" s="76"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="76" t="s">
         <v>380</v>
       </c>
@@ -19945,7 +19945,7 @@
       </c>
       <c r="S5" s="76"/>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="76" t="s">
         <v>380</v>
       </c>
@@ -20002,7 +20002,7 @@
       </c>
       <c r="S6" s="76"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="76" t="s">
         <v>323</v>
       </c>
@@ -20057,7 +20057,7 @@
       <c r="R7" s="76"/>
       <c r="S7" s="76"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="76" t="s">
         <v>250</v>
       </c>
@@ -20114,7 +20114,7 @@
       </c>
       <c r="S8" s="76"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="76" t="s">
         <v>250</v>
       </c>
@@ -20163,7 +20163,7 @@
       </c>
       <c r="S9" s="76"/>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="76" t="s">
         <v>250</v>
       </c>
@@ -20212,7 +20212,7 @@
       </c>
       <c r="S10" s="76"/>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="76" t="s">
         <v>380</v>
       </c>
@@ -20261,7 +20261,7 @@
       </c>
       <c r="S11" s="76"/>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="76" t="s">
         <v>315</v>
       </c>
@@ -20310,7 +20310,7 @@
       </c>
       <c r="S12" s="76"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="76" t="s">
         <v>269</v>
       </c>
@@ -20349,7 +20349,7 @@
       </c>
       <c r="S13" s="76"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="76" t="s">
         <v>369</v>
       </c>
@@ -20408,7 +20408,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="76" t="s">
         <v>281</v>
       </c>
@@ -20465,7 +20465,7 @@
       </c>
       <c r="S15" s="76"/>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="76" t="s">
         <v>281</v>
       </c>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="S16" s="76"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="76" t="s">
         <v>237</v>
       </c>
@@ -20563,7 +20563,7 @@
       </c>
       <c r="S17" s="76"/>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="76" t="s">
         <v>250</v>
       </c>
@@ -20612,7 +20612,7 @@
       </c>
       <c r="S18" s="76"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="76" t="s">
         <v>309</v>
       </c>
@@ -20663,7 +20663,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="76" t="s">
         <v>237</v>
       </c>
@@ -20712,7 +20712,7 @@
       </c>
       <c r="S20" s="113"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="76" t="s">
         <v>250</v>
       </c>
@@ -20771,7 +20771,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="76" t="s">
         <v>250</v>
       </c>
@@ -20820,7 +20820,7 @@
       </c>
       <c r="S22" s="76"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="76" t="s">
         <v>202</v>
       </c>
@@ -20879,7 +20879,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="76" t="s">
         <v>339</v>
       </c>
@@ -20936,7 +20936,7 @@
       </c>
       <c r="S24" s="76"/>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="76" t="s">
         <v>315</v>
       </c>
@@ -20985,7 +20985,7 @@
       </c>
       <c r="S25" s="76"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="76" t="s">
         <v>326</v>
       </c>
@@ -21022,7 +21022,7 @@
       </c>
       <c r="S26" s="76"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="76" t="s">
         <v>380</v>
       </c>
@@ -21071,7 +21071,7 @@
       </c>
       <c r="S27" s="76"/>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="76" t="s">
         <v>292</v>
       </c>
@@ -21130,7 +21130,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="76" t="s">
         <v>380</v>
       </c>
@@ -21179,7 +21179,7 @@
       </c>
       <c r="S29" s="76"/>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="76" t="s">
         <v>339</v>
       </c>
@@ -21238,7 +21238,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="76" t="s">
         <v>305</v>
       </c>
@@ -21297,7 +21297,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="76" t="s">
         <v>332</v>
       </c>
@@ -21356,7 +21356,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="76" t="s">
         <v>348</v>
       </c>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="S33" s="76"/>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="76" t="s">
         <v>348</v>
       </c>
@@ -21452,7 +21452,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="76" t="s">
         <v>348</v>
       </c>
@@ -21499,7 +21499,7 @@
       </c>
       <c r="S35" s="76"/>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="76" t="s">
         <v>348</v>
       </c>
@@ -21554,7 +21554,7 @@
       </c>
       <c r="S36" s="76"/>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="76" t="s">
         <v>348</v>
       </c>
@@ -21601,7 +21601,7 @@
       </c>
       <c r="S37" s="76"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="76" t="s">
         <v>348</v>
       </c>
@@ -21656,7 +21656,7 @@
       </c>
       <c r="S38" s="76"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="76" t="s">
         <v>261</v>
       </c>
@@ -21707,7 +21707,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="76" t="s">
         <v>261</v>
       </c>
@@ -21756,7 +21756,7 @@
       </c>
       <c r="S40" s="76"/>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="76" t="s">
         <v>261</v>
       </c>
@@ -21815,7 +21815,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="76" t="s">
         <v>332</v>
       </c>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="S42" s="76"/>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="76" t="s">
         <v>380</v>
       </c>
@@ -21929,7 +21929,7 @@
       </c>
       <c r="S43" s="76"/>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="76" t="s">
         <v>380</v>
       </c>
@@ -21978,7 +21978,7 @@
       </c>
       <c r="S44" s="76"/>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="76" t="s">
         <v>380</v>
       </c>
@@ -22027,7 +22027,7 @@
       </c>
       <c r="S45" s="76"/>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="76" t="s">
         <v>380</v>
       </c>
@@ -22076,7 +22076,7 @@
       </c>
       <c r="S46" s="76"/>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="76" t="s">
         <v>380</v>
       </c>
@@ -22125,7 +22125,7 @@
       </c>
       <c r="S47" s="76"/>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="76"/>
       <c r="B48" s="76"/>
       <c r="C48" s="76"/>
@@ -22146,7 +22146,7 @@
       <c r="R48" s="76"/>
       <c r="S48" s="76"/>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="76"/>
       <c r="B49" s="76"/>
       <c r="C49" s="76"/>
@@ -22167,7 +22167,7 @@
       <c r="R49" s="76"/>
       <c r="S49" s="76"/>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="76"/>
       <c r="B50" s="76"/>
       <c r="C50" s="76"/>
@@ -22218,9 +22218,9 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{412B20A3-E459-2846-B7BA-29FFD1AF0E4E}">
   <dimension ref="A1:S50"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="76" t="s">
         <v>4</v>
       </c>
@@ -22277,7 +22277,7 @@
       </c>
       <c r="S1" s="76"/>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="76" t="s">
         <v>281</v>
       </c>
@@ -22336,7 +22336,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="76" t="s">
         <v>202</v>
       </c>
@@ -22393,7 +22393,7 @@
       </c>
       <c r="S3" s="76"/>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="76" t="s">
         <v>223</v>
       </c>
@@ -22442,7 +22442,7 @@
       </c>
       <c r="S4" s="76"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="76" t="s">
         <v>380</v>
       </c>
@@ -22491,7 +22491,7 @@
       </c>
       <c r="S5" s="76"/>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="76" t="s">
         <v>380</v>
       </c>
@@ -22548,7 +22548,7 @@
       </c>
       <c r="S6" s="76"/>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="76" t="s">
         <v>323</v>
       </c>
@@ -22603,7 +22603,7 @@
       <c r="R7" s="76"/>
       <c r="S7" s="76"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="76" t="s">
         <v>250</v>
       </c>
@@ -22660,7 +22660,7 @@
       </c>
       <c r="S8" s="76"/>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="76" t="s">
         <v>250</v>
       </c>
@@ -22709,7 +22709,7 @@
       </c>
       <c r="S9" s="76"/>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="76" t="s">
         <v>250</v>
       </c>
@@ -22758,7 +22758,7 @@
       </c>
       <c r="S10" s="76"/>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="76" t="s">
         <v>380</v>
       </c>
@@ -22807,7 +22807,7 @@
       </c>
       <c r="S11" s="76"/>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="76" t="s">
         <v>315</v>
       </c>
@@ -22856,7 +22856,7 @@
       </c>
       <c r="S12" s="76"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="76" t="s">
         <v>269</v>
       </c>
@@ -22895,7 +22895,7 @@
       </c>
       <c r="S13" s="76"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="76" t="s">
         <v>369</v>
       </c>
@@ -22954,7 +22954,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="76" t="s">
         <v>281</v>
       </c>
@@ -23011,7 +23011,7 @@
       </c>
       <c r="S15" s="76"/>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="76" t="s">
         <v>281</v>
       </c>
@@ -23060,7 +23060,7 @@
       </c>
       <c r="S16" s="76"/>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="76" t="s">
         <v>237</v>
       </c>
@@ -23109,7 +23109,7 @@
       </c>
       <c r="S17" s="76"/>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="76" t="s">
         <v>250</v>
       </c>
@@ -23158,7 +23158,7 @@
       </c>
       <c r="S18" s="76"/>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="76" t="s">
         <v>309</v>
       </c>
@@ -23209,7 +23209,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="76" t="s">
         <v>237</v>
       </c>
@@ -23258,7 +23258,7 @@
       </c>
       <c r="S20" s="113"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="76" t="s">
         <v>250</v>
       </c>
@@ -23317,7 +23317,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="76" t="s">
         <v>250</v>
       </c>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="S22" s="76"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="76" t="s">
         <v>202</v>
       </c>
@@ -23425,7 +23425,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="76" t="s">
         <v>339</v>
       </c>
@@ -23482,7 +23482,7 @@
       </c>
       <c r="S24" s="76"/>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="76" t="s">
         <v>315</v>
       </c>
@@ -23531,7 +23531,7 @@
       </c>
       <c r="S25" s="76"/>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="76" t="s">
         <v>326</v>
       </c>
@@ -23568,7 +23568,7 @@
       </c>
       <c r="S26" s="76"/>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="76" t="s">
         <v>380</v>
       </c>
@@ -23617,7 +23617,7 @@
       </c>
       <c r="S27" s="76"/>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="76" t="s">
         <v>292</v>
       </c>
@@ -23676,7 +23676,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="76" t="s">
         <v>380</v>
       </c>
@@ -23725,7 +23725,7 @@
       </c>
       <c r="S29" s="76"/>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="76" t="s">
         <v>339</v>
       </c>
@@ -23784,7 +23784,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="76" t="s">
         <v>305</v>
       </c>
@@ -23843,7 +23843,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="76" t="s">
         <v>332</v>
       </c>
@@ -23902,7 +23902,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="76" t="s">
         <v>348</v>
       </c>
@@ -23949,7 +23949,7 @@
       </c>
       <c r="S33" s="76"/>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="76" t="s">
         <v>348</v>
       </c>
@@ -23998,7 +23998,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="76" t="s">
         <v>348</v>
       </c>
@@ -24045,7 +24045,7 @@
       </c>
       <c r="S35" s="76"/>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="76" t="s">
         <v>348</v>
       </c>
@@ -24100,7 +24100,7 @@
       </c>
       <c r="S36" s="76"/>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="76" t="s">
         <v>348</v>
       </c>
@@ -24147,7 +24147,7 @@
       </c>
       <c r="S37" s="76"/>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="76" t="s">
         <v>348</v>
       </c>
@@ -24202,7 +24202,7 @@
       </c>
       <c r="S38" s="76"/>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="76" t="s">
         <v>261</v>
       </c>
@@ -24253,7 +24253,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="76" t="s">
         <v>261</v>
       </c>
@@ -24302,7 +24302,7 @@
       </c>
       <c r="S40" s="76"/>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="76" t="s">
         <v>261</v>
       </c>
@@ -24361,7 +24361,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" s="76" t="s">
         <v>332</v>
       </c>
@@ -24418,7 +24418,7 @@
       </c>
       <c r="S42" s="76"/>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="76" t="s">
         <v>380</v>
       </c>
@@ -24475,7 +24475,7 @@
       </c>
       <c r="S43" s="76"/>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" s="76" t="s">
         <v>380</v>
       </c>
@@ -24524,7 +24524,7 @@
       </c>
       <c r="S44" s="76"/>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" s="76" t="s">
         <v>380</v>
       </c>
@@ -24573,7 +24573,7 @@
       </c>
       <c r="S45" s="76"/>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" s="76" t="s">
         <v>380</v>
       </c>
@@ -24622,7 +24622,7 @@
       </c>
       <c r="S46" s="76"/>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" s="76" t="s">
         <v>380</v>
       </c>
@@ -24671,7 +24671,7 @@
       </c>
       <c r="S47" s="76"/>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" s="76"/>
       <c r="B48" s="76"/>
       <c r="C48" s="76"/>
@@ -24692,7 +24692,7 @@
       <c r="R48" s="76"/>
       <c r="S48" s="76"/>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A49" s="76"/>
       <c r="B49" s="76"/>
       <c r="C49" s="76"/>
@@ -24713,7 +24713,7 @@
       <c r="R49" s="76"/>
       <c r="S49" s="76"/>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A50" s="76"/>
       <c r="B50" s="76"/>
       <c r="C50" s="76"/>
@@ -24763,12 +24763,12 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1996484-BAD8-A64B-B5F1-8D51E77CF113}">
   <dimension ref="A1:S48"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>431</v>
       </c>
@@ -24785,7 +24785,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -24841,7 +24841,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>281</v>
       </c>
@@ -24900,7 +24900,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>202</v>
       </c>
@@ -24956,7 +24956,7 @@
         <v>2110761</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>223</v>
       </c>
@@ -24998,7 +24998,7 @@
         <v>3650000</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>380</v>
       </c>
@@ -25046,7 +25046,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>380</v>
       </c>
@@ -25102,7 +25102,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>323</v>
       </c>
@@ -25152,7 +25152,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>250</v>
       </c>
@@ -25208,7 +25208,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>250</v>
       </c>
@@ -25256,7 +25256,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>250</v>
       </c>
@@ -25304,7 +25304,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>380</v>
       </c>
@@ -25352,7 +25352,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>315</v>
       </c>
@@ -25400,7 +25400,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>269</v>
       </c>
@@ -25433,7 +25433,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>369</v>
       </c>
@@ -25489,7 +25489,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>281</v>
       </c>
@@ -25545,7 +25545,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>281</v>
       </c>
@@ -25593,7 +25593,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>237</v>
       </c>
@@ -25641,7 +25641,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>250</v>
       </c>
@@ -25689,7 +25689,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>309</v>
       </c>
@@ -25740,7 +25740,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>237</v>
       </c>
@@ -25788,7 +25788,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>250</v>
       </c>
@@ -25847,7 +25847,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>250</v>
       </c>
@@ -25895,7 +25895,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>202</v>
       </c>
@@ -25954,7 +25954,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>339</v>
       </c>
@@ -26010,7 +26010,7 @@
         <v>39140033.75</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>315</v>
       </c>
@@ -26058,7 +26058,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>326</v>
       </c>
@@ -26084,7 +26084,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>380</v>
       </c>
@@ -26131,7 +26131,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>292</v>
       </c>
@@ -26187,7 +26187,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>380</v>
       </c>
@@ -26234,7 +26234,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>339</v>
       </c>
@@ -26293,7 +26293,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>305</v>
       </c>
@@ -26352,7 +26352,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>332</v>
       </c>
@@ -26411,7 +26411,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>348</v>
       </c>
@@ -26456,7 +26456,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>348</v>
       </c>
@@ -26504,7 +26504,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>348</v>
       </c>
@@ -26549,7 +26549,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>348</v>
       </c>
@@ -26602,7 +26602,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>348</v>
       </c>
@@ -26647,7 +26647,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>348</v>
       </c>
@@ -26700,7 +26700,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>261</v>
       </c>
@@ -26748,7 +26748,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>261</v>
       </c>
@@ -26793,7 +26793,7 @@
         <v>58035000</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>261</v>
       </c>
@@ -26849,7 +26849,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" s="76" t="s">
         <v>332</v>
       </c>
@@ -26905,7 +26905,7 @@
         <v>1250000000</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>380</v>
       </c>
@@ -26961,7 +26961,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>380</v>
       </c>
@@ -27005,7 +27005,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>380</v>
       </c>
@@ -27049,7 +27049,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>380</v>
       </c>
@@ -27093,7 +27093,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>380</v>
       </c>
@@ -27145,19 +27145,19 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DD39D0D-2E00-C947-B5B6-B50788BBBD42}">
   <dimension ref="A1:S51"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="12" max="18" width="18.25" customWidth="1"/>
+    <col min="10" max="10" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="18" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -27213,7 +27213,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>281</v>
       </c>
@@ -27272,7 +27272,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>202</v>
       </c>
@@ -27328,7 +27328,7 @@
         <v>2110761</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>223</v>
       </c>
@@ -27376,7 +27376,7 @@
         <v>3650000</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>380</v>
       </c>
@@ -27420,7 +27420,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>380</v>
       </c>
@@ -27476,7 +27476,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>323</v>
       </c>
@@ -27530,7 +27530,7 @@
       </c>
       <c r="R7" s="13"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>250</v>
       </c>
@@ -27586,7 +27586,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>250</v>
       </c>
@@ -27634,7 +27634,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>250</v>
       </c>
@@ -27682,7 +27682,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>380</v>
       </c>
@@ -27726,7 +27726,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>315</v>
       </c>
@@ -27774,7 +27774,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>269</v>
       </c>
@@ -27811,7 +27811,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>369</v>
       </c>
@@ -27870,7 +27870,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>281</v>
       </c>
@@ -27926,7 +27926,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>281</v>
       </c>
@@ -27974,7 +27974,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>237</v>
       </c>
@@ -28022,7 +28022,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>250</v>
       </c>
@@ -28070,7 +28070,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>309</v>
       </c>
@@ -28121,7 +28121,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>237</v>
       </c>
@@ -28170,7 +28170,7 @@
       </c>
       <c r="S20" s="20"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>250</v>
       </c>
@@ -28229,7 +28229,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>250</v>
       </c>
@@ -28277,7 +28277,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>202</v>
       </c>
@@ -28336,7 +28336,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>339</v>
       </c>
@@ -28392,7 +28392,7 @@
         <v>39140033.75</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>315</v>
       </c>
@@ -28440,7 +28440,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>326</v>
       </c>
@@ -28470,7 +28470,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="16.899999999999999" customHeight="1">
+    <row r="27" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>380</v>
       </c>
@@ -28514,7 +28514,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="16.899999999999999" customHeight="1">
+    <row r="28" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>292</v>
       </c>
@@ -28573,7 +28573,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>380</v>
       </c>
@@ -28617,7 +28617,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>339</v>
       </c>
@@ -28676,7 +28676,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>305</v>
       </c>
@@ -28735,7 +28735,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>332</v>
       </c>
@@ -28794,7 +28794,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>348</v>
       </c>
@@ -28839,7 +28839,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>348</v>
       </c>
@@ -28887,7 +28887,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>348</v>
       </c>
@@ -28932,7 +28932,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>348</v>
       </c>
@@ -28985,7 +28985,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>348</v>
       </c>
@@ -29030,7 +29030,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>348</v>
       </c>
@@ -29083,7 +29083,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>261</v>
       </c>
@@ -29134,7 +29134,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>261</v>
       </c>
@@ -29182,7 +29182,7 @@
         <v>58035000</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>261</v>
       </c>
@@ -29241,7 +29241,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>332</v>
       </c>
@@ -29297,7 +29297,7 @@
         <v>1250000000</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>380</v>
       </c>
@@ -29353,7 +29353,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>380</v>
       </c>
@@ -29397,7 +29397,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>380</v>
       </c>
@@ -29441,7 +29441,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>380</v>
       </c>
@@ -29485,7 +29485,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>380</v>
       </c>
@@ -29529,7 +29529,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="H48" s="75"/>
       <c r="I48" s="75"/>
       <c r="J48" s="75"/>
@@ -29538,13 +29538,13 @@
       <c r="Q48" s="12"/>
       <c r="R48" s="86"/>
     </row>
-    <row r="49" spans="8:11">
+    <row r="49" spans="8:11" x14ac:dyDescent="0.2">
       <c r="H49" s="75"/>
       <c r="I49" s="75"/>
       <c r="J49" s="75"/>
       <c r="K49" s="75"/>
     </row>
-    <row r="51" spans="8:11">
+    <row r="51" spans="8:11" x14ac:dyDescent="0.2">
       <c r="H51" s="75"/>
       <c r="I51" s="75"/>
     </row>
@@ -29578,7 +29578,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06161075-588E-5843-BB7A-EDB11B09427F}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -29587,17 +29587,17 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E835E82-8D33-444A-BB8C-C24845EF2DC0}">
   <dimension ref="A1:S51"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="16" width="18.25" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="16" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -29653,7 +29653,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>281</v>
       </c>
@@ -29712,7 +29712,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>202</v>
       </c>
@@ -29768,7 +29768,7 @@
         <v>2110761</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>223</v>
       </c>
@@ -29816,7 +29816,7 @@
         <v>3650000</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>380</v>
       </c>
@@ -29860,7 +29860,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>380</v>
       </c>
@@ -29916,7 +29916,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>323</v>
       </c>
@@ -29970,7 +29970,7 @@
       </c>
       <c r="R7" s="13"/>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>250</v>
       </c>
@@ -30026,7 +30026,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>250</v>
       </c>
@@ -30074,7 +30074,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>250</v>
       </c>
@@ -30122,7 +30122,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>380</v>
       </c>
@@ -30166,7 +30166,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>315</v>
       </c>
@@ -30214,7 +30214,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>269</v>
       </c>
@@ -30251,7 +30251,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>369</v>
       </c>
@@ -30310,7 +30310,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>281</v>
       </c>
@@ -30366,7 +30366,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>281</v>
       </c>
@@ -30414,7 +30414,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>237</v>
       </c>
@@ -30462,7 +30462,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>250</v>
       </c>
@@ -30510,7 +30510,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>309</v>
       </c>
@@ -30561,7 +30561,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>237</v>
       </c>
@@ -30610,7 +30610,7 @@
       </c>
       <c r="S20" s="20"/>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>250</v>
       </c>
@@ -30669,7 +30669,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>250</v>
       </c>
@@ -30717,7 +30717,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>202</v>
       </c>
@@ -30776,7 +30776,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>339</v>
       </c>
@@ -30832,7 +30832,7 @@
         <v>39140033.75</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>315</v>
       </c>
@@ -30880,7 +30880,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>326</v>
       </c>
@@ -30910,7 +30910,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>380</v>
       </c>
@@ -30954,7 +30954,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="16.899999999999999" customHeight="1">
+    <row r="28" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>292</v>
       </c>
@@ -31013,7 +31013,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="16.899999999999999" customHeight="1">
+    <row r="29" spans="1:19" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>380</v>
       </c>
@@ -31057,7 +31057,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>339</v>
       </c>
@@ -31116,7 +31116,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>305</v>
       </c>
@@ -31175,7 +31175,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>332</v>
       </c>
@@ -31234,7 +31234,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>348</v>
       </c>
@@ -31279,7 +31279,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>348</v>
       </c>
@@ -31327,7 +31327,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>348</v>
       </c>
@@ -31372,7 +31372,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>348</v>
       </c>
@@ -31425,7 +31425,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>348</v>
       </c>
@@ -31470,7 +31470,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>348</v>
       </c>
@@ -31523,7 +31523,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>261</v>
       </c>
@@ -31574,7 +31574,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>261</v>
       </c>
@@ -31622,7 +31622,7 @@
         <v>58035000</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>261</v>
       </c>
@@ -31681,7 +31681,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>332</v>
       </c>
@@ -31737,7 +31737,7 @@
         <v>1250000000</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>380</v>
       </c>
@@ -31793,7 +31793,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>380</v>
       </c>
@@ -31837,7 +31837,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>380</v>
       </c>
@@ -31881,7 +31881,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>380</v>
       </c>
@@ -31925,7 +31925,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>380</v>
       </c>
@@ -31969,7 +31969,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.2">
       <c r="F48" s="75"/>
       <c r="G48" s="75"/>
       <c r="H48" s="75"/>
@@ -31978,13 +31978,13 @@
       <c r="O48" s="12"/>
       <c r="P48" s="86"/>
     </row>
-    <row r="49" spans="6:9">
+    <row r="49" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F49" s="75"/>
       <c r="G49" s="75"/>
       <c r="H49" s="75"/>
       <c r="I49" s="75"/>
     </row>
-    <row r="51" spans="6:9">
+    <row r="51" spans="6:9" x14ac:dyDescent="0.2">
       <c r="F51" s="75"/>
       <c r="G51" s="75"/>
     </row>
@@ -32017,12 +32017,12 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA0C7AF6-12B8-E94C-86EE-0E1EAB47201C}">
   <dimension ref="A1:T47"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="19" max="19" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -32081,7 +32081,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>281</v>
       </c>
@@ -32144,7 +32144,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="3" spans="1:20">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>202</v>
       </c>
@@ -32204,7 +32204,7 @@
         <v>2110761</v>
       </c>
     </row>
-    <row r="4" spans="1:20">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>223</v>
       </c>
@@ -32256,7 +32256,7 @@
         <v>3650000</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>380</v>
       </c>
@@ -32304,7 +32304,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>380</v>
       </c>
@@ -32364,7 +32364,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>323</v>
       </c>
@@ -32421,7 +32421,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>250</v>
       </c>
@@ -32481,7 +32481,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>250</v>
       </c>
@@ -32533,7 +32533,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>250</v>
       </c>
@@ -32585,7 +32585,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>380</v>
       </c>
@@ -32633,7 +32633,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="12" spans="1:20">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>315</v>
       </c>
@@ -32685,7 +32685,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:20">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>269</v>
       </c>
@@ -32723,7 +32723,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>369</v>
       </c>
@@ -32786,7 +32786,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>281</v>
       </c>
@@ -32846,7 +32846,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>281</v>
       </c>
@@ -32898,7 +32898,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>237</v>
       </c>
@@ -32950,7 +32950,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>250</v>
       </c>
@@ -33002,7 +33002,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>309</v>
       </c>
@@ -33057,7 +33057,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>237</v>
       </c>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="T20" s="20"/>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>250</v>
       </c>
@@ -33173,7 +33173,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>250</v>
       </c>
@@ -33225,7 +33225,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>202</v>
       </c>
@@ -33288,7 +33288,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>339</v>
       </c>
@@ -33348,7 +33348,7 @@
         <v>39140033.75</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>315</v>
       </c>
@@ -33400,7 +33400,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>326</v>
       </c>
@@ -33431,7 +33431,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:20">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>380</v>
       </c>
@@ -33479,7 +33479,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="28" spans="1:20">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>292</v>
       </c>
@@ -33542,7 +33542,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="29" spans="1:20">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>380</v>
       </c>
@@ -33590,7 +33590,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>339</v>
       </c>
@@ -33653,7 +33653,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>305</v>
       </c>
@@ -33716,7 +33716,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="32" spans="1:20">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>332</v>
       </c>
@@ -33779,7 +33779,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="33" spans="1:20">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>348</v>
       </c>
@@ -33828,7 +33828,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>348</v>
       </c>
@@ -33880,7 +33880,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="35" spans="1:20">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>348</v>
       </c>
@@ -33929,7 +33929,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="36" spans="1:20">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>348</v>
       </c>
@@ -33986,7 +33986,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>348</v>
       </c>
@@ -34035,7 +34035,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>348</v>
       </c>
@@ -34092,7 +34092,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>261</v>
       </c>
@@ -34147,7 +34147,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="40" spans="1:20">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>261</v>
       </c>
@@ -34199,7 +34199,7 @@
         <v>58035000</v>
       </c>
     </row>
-    <row r="41" spans="1:20">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>261</v>
       </c>
@@ -34262,7 +34262,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="42" spans="1:20">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>332</v>
       </c>
@@ -34322,7 +34322,7 @@
         <v>1250000000</v>
       </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>380</v>
       </c>
@@ -34382,7 +34382,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="44" spans="1:20">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>380</v>
       </c>
@@ -34430,7 +34430,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>380</v>
       </c>
@@ -34478,7 +34478,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>380</v>
       </c>
@@ -34526,7 +34526,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>380</v>
       </c>
@@ -34584,15 +34584,15 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{981DCFE0-9FB2-D14D-9941-0D6BF8A04E8E}">
   <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="126">
         <v>2024</v>
       </c>
@@ -34602,7 +34602,7 @@
       </c>
       <c r="E1" s="126"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>435</v>
       </c>
@@ -34630,18 +34630,18 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{456C42C4-6099-164A-8598-EED346428AD2}">
   <dimension ref="A1:M27"/>
-  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="34.5" style="21" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.25" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="15.25" style="21" customWidth="1"/>
-    <col min="8" max="12" width="10.75" style="21"/>
-    <col min="13" max="13" width="11.75" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="15.1640625" style="21" customWidth="1"/>
+    <col min="8" max="12" width="10.6640625" style="21"/>
+    <col min="13" max="13" width="11.6640625" style="21" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" style="21" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="10.75" style="21"/>
+    <col min="15" max="16384" width="10.6640625" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>5</v>
       </c>
@@ -34678,7 +34678,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>446</v>
       </c>
@@ -34729,7 +34729,7 @@
         <v>400.57</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>447</v>
       </c>
@@ -34780,7 +34780,7 @@
         <v>958.49999999999989</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>448</v>
       </c>
@@ -34831,7 +34831,7 @@
         <v>17.91</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>449</v>
       </c>
@@ -34882,7 +34882,7 @@
         <v>26.24</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>450</v>
       </c>
@@ -34933,7 +34933,7 @@
         <v>13.76</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>451</v>
       </c>
@@ -34984,7 +34984,7 @@
         <v>2.98</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>452</v>
       </c>
@@ -35035,7 +35035,7 @@
         <v>7.51</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>453</v>
       </c>
@@ -35086,7 +35086,7 @@
         <v>8.8699999999999992</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>454</v>
       </c>
@@ -35137,7 +35137,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>455</v>
       </c>
@@ -35188,7 +35188,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="12" spans="1:13">
+    <row r="12" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="123" t="s">
         <v>456</v>
       </c>
@@ -35239,7 +35239,7 @@
         <v>36.36</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="123" t="s">
         <v>457</v>
       </c>
@@ -35286,7 +35286,7 @@
         <v>1485.4999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14" s="116"/>
       <c r="B14" s="116"/>
       <c r="C14" s="116"/>
@@ -35319,7 +35319,7 @@
         <v>1672.9142738166718</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="16.899999999999999" customHeight="1">
+    <row r="15" spans="1:13" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>458</v>
       </c>
@@ -35339,7 +35339,7 @@
       <c r="L15" s="5"/>
       <c r="M15" s="5"/>
     </row>
-    <row r="16" spans="1:13">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" s="122"/>
       <c r="C16" s="122"/>
@@ -35354,7 +35354,7 @@
       <c r="L16" s="5"/>
       <c r="M16" s="5"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>459</v>
       </c>
@@ -35366,7 +35366,7 @@
       <c r="G17" s="122"/>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="121">
         <v>0.02</v>
       </c>
@@ -35384,7 +35384,7 @@
         <v>234.3</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="121">
         <v>0.1</v>
       </c>
@@ -35402,7 +35402,7 @@
         <v>319.5</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="121">
         <v>0.35</v>
       </c>
@@ -35420,7 +35420,7 @@
         <v>585.75</v>
       </c>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="121">
         <v>0.7</v>
       </c>
@@ -35438,7 +35438,7 @@
         <v>958.49999999999989</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="121">
         <v>1</v>
       </c>
@@ -35456,7 +35456,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" s="122"/>
       <c r="C23" s="122"/>
@@ -35466,7 +35466,7 @@
       <c r="G23" s="122"/>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
         <v>460</v>
       </c>
@@ -35478,7 +35478,7 @@
       <c r="G24" s="122"/>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" s="122"/>
       <c r="C25" s="122"/>
@@ -35488,7 +35488,7 @@
       <c r="G25" s="122"/>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" s="122"/>
       <c r="C26" s="122"/>
@@ -35498,7 +35498,7 @@
       <c r="G26" s="122"/>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="B27" s="122"/>
       <c r="C27" s="122"/>
@@ -35519,15 +35519,15 @@
     <tabColor theme="6" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.25" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -35541,7 +35541,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>5</v>
       </c>
@@ -35555,12 +35555,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="18" customFormat="1">
+    <row r="3" spans="1:5" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -35568,7 +35568,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -35576,7 +35576,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -35584,7 +35584,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>13</v>
       </c>
@@ -35592,12 +35592,12 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="18" customFormat="1">
+    <row r="8" spans="1:5" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>15</v>
       </c>
@@ -35612,7 +35612,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>15</v>
       </c>
@@ -35630,12 +35630,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:5" s="18" customFormat="1">
+    <row r="11" spans="1:5" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -35650,7 +35650,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -35665,7 +35665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -35677,7 +35677,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -35689,7 +35689,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -35701,7 +35701,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -35716,12 +35716,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:4" s="18" customFormat="1">
+    <row r="18" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>26</v>
       </c>
@@ -35736,12 +35736,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:4" s="14" customFormat="1">
+    <row r="20" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="19" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>26</v>
       </c>
@@ -35756,7 +35756,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>26</v>
       </c>
@@ -35771,12 +35771,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:4" s="14" customFormat="1">
+    <row r="23" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="19" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -35791,7 +35791,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -35806,12 +35806,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:4" s="14" customFormat="1">
+    <row r="26" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>26</v>
       </c>
@@ -35826,7 +35826,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>26</v>
       </c>
@@ -35841,12 +35841,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:4" s="14" customFormat="1">
+    <row r="29" spans="1:4" s="14" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>26</v>
       </c>
@@ -35861,7 +35861,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -35876,12 +35876,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:4" s="18" customFormat="1">
+    <row r="32" spans="1:4" s="18" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="17" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -35899,7 +35899,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>34</v>
       </c>
@@ -35933,17 +35933,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20E1155D-2A55-0744-BB3C-78DAEE3CB015}">
   <dimension ref="A1:AN40"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.25" customWidth="1"/>
-    <col min="2" max="2" width="20.25" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
+    <col min="2" max="2" width="20.1640625" customWidth="1"/>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="35" max="35" width="8.75" style="111"/>
-    <col min="36" max="36" width="17.25" style="101" customWidth="1"/>
-    <col min="37" max="37" width="13.75" customWidth="1"/>
+    <col min="35" max="35" width="8.6640625" style="111"/>
+    <col min="36" max="36" width="17.1640625" style="101" customWidth="1"/>
+    <col min="37" max="37" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:38">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A1" s="91" t="s">
         <v>37</v>
       </c>
@@ -36059,7 +36059,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:38">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A2" s="94" t="s">
         <v>45</v>
       </c>
@@ -36176,7 +36176,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="1:38">
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A3" s="100" t="s">
         <v>53</v>
       </c>
@@ -36283,7 +36283,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:38">
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A4" s="100" t="s">
         <v>55</v>
       </c>
@@ -36390,7 +36390,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:38">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="100" t="s">
         <v>57</v>
       </c>
@@ -36497,7 +36497,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:38">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A6" s="100" t="s">
         <v>58</v>
       </c>
@@ -36604,7 +36604,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:38">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A7" s="100" t="s">
         <v>59</v>
       </c>
@@ -36711,7 +36711,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:38">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A8" s="100" t="s">
         <v>60</v>
       </c>
@@ -36818,7 +36818,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:38">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A9" s="100" t="s">
         <v>61</v>
       </c>
@@ -36925,7 +36925,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:38">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A10" s="100" t="s">
         <v>62</v>
       </c>
@@ -37032,7 +37032,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:38">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A11" s="100" t="s">
         <v>63</v>
       </c>
@@ -37139,7 +37139,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:38">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" s="100" t="s">
         <v>64</v>
       </c>
@@ -37246,7 +37246,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:38">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A13" s="100" t="s">
         <v>65</v>
       </c>
@@ -37353,7 +37353,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="14" spans="1:38">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" s="94" t="s">
         <v>45</v>
       </c>
@@ -37470,7 +37470,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:38">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" s="100" t="s">
         <v>66</v>
       </c>
@@ -37577,7 +37577,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="16" spans="1:38">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16" s="100" t="s">
         <v>67</v>
       </c>
@@ -37684,7 +37684,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:38">
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17" s="100" t="s">
         <v>68</v>
       </c>
@@ -37791,7 +37791,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:38">
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18" s="100" t="s">
         <v>69</v>
       </c>
@@ -37898,7 +37898,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:38">
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19" s="100" t="s">
         <v>70</v>
       </c>
@@ -38015,7 +38015,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="20" spans="1:38">
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20" s="100" t="s">
         <v>53</v>
       </c>
@@ -38122,7 +38122,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:38">
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" s="100" t="s">
         <v>55</v>
       </c>
@@ -38229,7 +38229,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:38">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22" s="100" t="s">
         <v>57</v>
       </c>
@@ -38336,7 +38336,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:38">
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23" s="100" t="s">
         <v>58</v>
       </c>
@@ -38443,7 +38443,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="24" spans="1:38">
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24" s="100" t="s">
         <v>59</v>
       </c>
@@ -38550,7 +38550,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="1:38">
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A25" s="100" t="s">
         <v>60</v>
       </c>
@@ -38657,7 +38657,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:38">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A26" s="100" t="s">
         <v>61</v>
       </c>
@@ -38764,7 +38764,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:38">
+    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A27" s="100" t="s">
         <v>62</v>
       </c>
@@ -38871,7 +38871,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="28" spans="1:38">
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A28" s="100" t="s">
         <v>63</v>
       </c>
@@ -38978,7 +38978,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="1:38">
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A29" s="100" t="s">
         <v>64</v>
       </c>
@@ -39085,7 +39085,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="1:38">
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A30" s="100" t="s">
         <v>65</v>
       </c>
@@ -39192,7 +39192,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:38" s="10" customFormat="1">
+    <row r="31" spans="1:38" s="10" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="94" t="s">
         <v>45</v>
       </c>
@@ -39309,7 +39309,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="1:38">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A32" s="100" t="s">
         <v>66</v>
       </c>
@@ -39416,7 +39416,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:40">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A33" s="100" t="s">
         <v>67</v>
       </c>
@@ -39523,7 +39523,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:40">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A34" s="100" t="s">
         <v>68</v>
       </c>
@@ -39630,7 +39630,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:40">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A35" s="100" t="s">
         <v>69</v>
       </c>
@@ -39737,7 +39737,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:40">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A36" s="100" t="s">
         <v>70</v>
       </c>
@@ -39854,7 +39854,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="1:40" s="101" customFormat="1">
+    <row r="37" spans="1:40" s="101" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="107" t="s">
         <v>74</v>
       </c>
@@ -39881,7 +39881,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:40" s="101" customFormat="1">
+    <row r="38" spans="1:40" s="101" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="107" t="s">
         <v>74</v>
       </c>
@@ -39905,7 +39905,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:40" s="101" customFormat="1">
+    <row r="39" spans="1:40" s="101" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="107" t="s">
         <v>77</v>
       </c>
@@ -39938,7 +39938,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:40" s="101" customFormat="1">
+    <row r="40" spans="1:40" s="101" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A40" s="107" t="s">
         <v>77</v>
       </c>
@@ -39977,17 +39977,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C700A40-351E-EE4C-92AD-3BC93D7F11F0}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:AR115"/>
-  <sheetFormatPr defaultColWidth="10.75" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.75" style="23"/>
-    <col min="2" max="2" width="69.75" style="23" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" style="23"/>
+    <col min="2" max="2" width="69.6640625" style="23" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.75" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" style="23" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.5" style="23" customWidth="1"/>
-    <col min="6" max="16384" width="10.75" style="23"/>
+    <col min="6" max="16384" width="10.6640625" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A1" s="22"/>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -40033,7 +40033,7 @@
       <c r="AQ1" s="22"/>
       <c r="AR1" s="22"/>
     </row>
-    <row r="2" spans="1:44" ht="20.45" thickBot="1">
+    <row r="2" spans="1:44" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="22"/>
       <c r="B2" s="24" t="s">
         <v>81</v>
@@ -40081,7 +40081,7 @@
       <c r="AQ2" s="22"/>
       <c r="AR2" s="22"/>
     </row>
-    <row r="3" spans="1:44" ht="16.149999999999999" thickTop="1">
+    <row r="3" spans="1:44" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="22"/>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -40127,7 +40127,7 @@
       <c r="AQ3" s="22"/>
       <c r="AR3" s="22"/>
     </row>
-    <row r="4" spans="1:44">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="22"/>
       <c r="B4" s="23" t="s">
         <v>82</v>
@@ -40177,7 +40177,7 @@
       <c r="AQ4" s="22"/>
       <c r="AR4" s="22"/>
     </row>
-    <row r="5" spans="1:44">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="22"/>
       <c r="B5" s="22" t="s">
         <v>6</v>
@@ -40285,7 +40285,7 @@
       <c r="AQ5" s="28"/>
       <c r="AR5" s="28"/>
     </row>
-    <row r="6" spans="1:44">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="29"/>
       <c r="B6" s="29" t="s">
         <v>85</v>
@@ -40391,7 +40391,7 @@
       <c r="AQ6" s="32"/>
       <c r="AR6" s="32"/>
     </row>
-    <row r="7" spans="1:44">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="33"/>
       <c r="B7" s="33" t="s">
         <v>86</v>
@@ -40497,7 +40497,7 @@
       <c r="AQ7" s="37"/>
       <c r="AR7" s="37"/>
     </row>
-    <row r="8" spans="1:44">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="25"/>
       <c r="B8" s="25"/>
       <c r="C8" s="38"/>
@@ -40543,7 +40543,7 @@
       <c r="AQ8" s="38"/>
       <c r="AR8" s="38"/>
     </row>
-    <row r="9" spans="1:44">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="25"/>
       <c r="B9" s="25" t="s">
         <v>87</v>
@@ -40591,7 +40591,7 @@
       <c r="AQ9" s="38"/>
       <c r="AR9" s="38"/>
     </row>
-    <row r="10" spans="1:44">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="25"/>
       <c r="B10" s="25" t="s">
         <v>88</v>
@@ -40639,7 +40639,7 @@
       <c r="AQ10" s="38"/>
       <c r="AR10" s="38"/>
     </row>
-    <row r="11" spans="1:44">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="25"/>
       <c r="B11" s="25" t="s">
         <v>89</v>
@@ -40745,7 +40745,7 @@
       <c r="AQ11" s="38"/>
       <c r="AR11" s="38"/>
     </row>
-    <row r="12" spans="1:44">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A12" s="25"/>
       <c r="B12" s="25" t="s">
         <v>90</v>
@@ -40793,7 +40793,7 @@
       <c r="AQ12" s="38"/>
       <c r="AR12" s="38"/>
     </row>
-    <row r="13" spans="1:44">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A13" s="22"/>
       <c r="B13" s="25" t="s">
         <v>89</v>
@@ -40899,7 +40899,7 @@
       <c r="AQ13" s="22"/>
       <c r="AR13" s="22"/>
     </row>
-    <row r="14" spans="1:44">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A14" s="22"/>
       <c r="B14" s="25" t="s">
         <v>91</v>
@@ -40947,7 +40947,7 @@
       <c r="AQ14" s="22"/>
       <c r="AR14" s="22"/>
     </row>
-    <row r="15" spans="1:44">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A15" s="22"/>
       <c r="B15" s="25" t="s">
         <v>89</v>
@@ -41053,7 +41053,7 @@
       <c r="AQ15" s="22"/>
       <c r="AR15" s="22"/>
     </row>
-    <row r="16" spans="1:44">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A16" s="22"/>
       <c r="B16" s="22"/>
       <c r="C16" s="38"/>
@@ -41099,7 +41099,7 @@
       <c r="AQ16" s="22"/>
       <c r="AR16" s="22"/>
     </row>
-    <row r="17" spans="1:44">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A17" s="22"/>
       <c r="B17" s="22"/>
       <c r="C17" s="38"/>
@@ -41143,7 +41143,7 @@
       <c r="AQ17" s="22"/>
       <c r="AR17" s="22"/>
     </row>
-    <row r="18" spans="1:44" ht="20.45" thickBot="1">
+    <row r="18" spans="1:44" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="22"/>
       <c r="B18" s="24" t="s">
         <v>92</v>
@@ -41195,7 +41195,7 @@
       <c r="AQ18" s="22"/>
       <c r="AR18" s="22"/>
     </row>
-    <row r="19" spans="1:44" ht="16.149999999999999" thickTop="1">
+    <row r="19" spans="1:44" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A19" s="22"/>
       <c r="B19" s="22"/>
       <c r="C19" s="22"/>
@@ -41245,7 +41245,7 @@
       <c r="AQ19" s="22"/>
       <c r="AR19" s="22"/>
     </row>
-    <row r="20" spans="1:44">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A20" s="22"/>
       <c r="B20" s="22"/>
       <c r="C20" s="22" t="s">
@@ -41297,7 +41297,7 @@
       <c r="AQ20" s="22"/>
       <c r="AR20" s="22"/>
     </row>
-    <row r="21" spans="1:44">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A21" s="22"/>
       <c r="B21" s="40" t="s">
         <v>98</v>
@@ -41351,7 +41351,7 @@
       <c r="AQ21" s="22"/>
       <c r="AR21" s="22"/>
     </row>
-    <row r="22" spans="1:44">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A22" s="22"/>
       <c r="B22" s="40" t="s">
         <v>99</v>
@@ -41405,7 +41405,7 @@
       <c r="AQ22" s="22"/>
       <c r="AR22" s="22"/>
     </row>
-    <row r="23" spans="1:44">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A23" s="22"/>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -41451,7 +41451,7 @@
       <c r="AQ23" s="22"/>
       <c r="AR23" s="22"/>
     </row>
-    <row r="24" spans="1:44">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A24" s="22"/>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -41497,7 +41497,7 @@
       <c r="AQ24" s="22"/>
       <c r="AR24" s="22"/>
     </row>
-    <row r="25" spans="1:44">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A25" s="22"/>
       <c r="B25" s="22" t="s">
         <v>6</v>
@@ -41549,7 +41549,7 @@
       <c r="AQ25" s="22"/>
       <c r="AR25" s="22"/>
     </row>
-    <row r="26" spans="1:44">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A26" s="22"/>
       <c r="B26" s="22"/>
       <c r="C26" s="46"/>
@@ -41595,7 +41595,7 @@
       <c r="AQ26" s="22"/>
       <c r="AR26" s="22"/>
     </row>
-    <row r="27" spans="1:44">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A27" s="22"/>
       <c r="B27" s="47" t="s">
         <v>95</v>
@@ -41643,7 +41643,7 @@
       <c r="AQ27" s="22"/>
       <c r="AR27" s="22"/>
     </row>
-    <row r="28" spans="1:44">
+    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A28" s="22"/>
       <c r="B28" s="22" t="s">
         <v>100</v>
@@ -41695,7 +41695,7 @@
       <c r="AQ28" s="49"/>
       <c r="AR28" s="49"/>
     </row>
-    <row r="29" spans="1:44">
+    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A29" s="22"/>
       <c r="B29" s="22" t="s">
         <v>101</v>
@@ -41747,7 +41747,7 @@
       <c r="AQ29" s="49"/>
       <c r="AR29" s="49"/>
     </row>
-    <row r="30" spans="1:44">
+    <row r="30" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A30" s="22"/>
       <c r="B30" s="22" t="s">
         <v>102</v>
@@ -41799,7 +41799,7 @@
       <c r="AQ30" s="22"/>
       <c r="AR30" s="22"/>
     </row>
-    <row r="31" spans="1:44">
+    <row r="31" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A31" s="22"/>
       <c r="B31" s="22" t="s">
         <v>103</v>
@@ -41851,7 +41851,7 @@
       <c r="AQ31" s="22"/>
       <c r="AR31" s="22"/>
     </row>
-    <row r="32" spans="1:44">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A32" s="22"/>
       <c r="B32" s="22"/>
       <c r="C32" s="22"/>
@@ -41897,7 +41897,7 @@
       <c r="AQ32" s="22"/>
       <c r="AR32" s="22"/>
     </row>
-    <row r="33" spans="1:44">
+    <row r="33" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A33" s="22"/>
       <c r="B33" s="47" t="s">
         <v>96</v>
@@ -41945,7 +41945,7 @@
       <c r="AQ33" s="46"/>
       <c r="AR33" s="46"/>
     </row>
-    <row r="34" spans="1:44">
+    <row r="34" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A34" s="22"/>
       <c r="B34" s="22" t="s">
         <v>100</v>
@@ -41997,7 +41997,7 @@
       <c r="AQ34" s="49"/>
       <c r="AR34" s="49"/>
     </row>
-    <row r="35" spans="1:44">
+    <row r="35" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A35" s="22"/>
       <c r="B35" s="22" t="s">
         <v>101</v>
@@ -42049,7 +42049,7 @@
       <c r="AQ35" s="49"/>
       <c r="AR35" s="49"/>
     </row>
-    <row r="36" spans="1:44">
+    <row r="36" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A36" s="22"/>
       <c r="B36" s="22" t="s">
         <v>102</v>
@@ -42101,7 +42101,7 @@
       <c r="AQ36" s="22"/>
       <c r="AR36" s="22"/>
     </row>
-    <row r="37" spans="1:44">
+    <row r="37" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A37" s="22"/>
       <c r="B37" s="22" t="s">
         <v>103</v>
@@ -42153,7 +42153,7 @@
       <c r="AQ37" s="22"/>
       <c r="AR37" s="22"/>
     </row>
-    <row r="38" spans="1:44">
+    <row r="38" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A38" s="22"/>
       <c r="B38" s="22"/>
       <c r="C38" s="22"/>
@@ -42199,7 +42199,7 @@
       <c r="AQ38" s="22"/>
       <c r="AR38" s="22"/>
     </row>
-    <row r="39" spans="1:44">
+    <row r="39" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A39" s="22"/>
       <c r="B39" s="47" t="s">
         <v>97</v>
@@ -42247,7 +42247,7 @@
       <c r="AQ39" s="22"/>
       <c r="AR39" s="22"/>
     </row>
-    <row r="40" spans="1:44">
+    <row r="40" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A40" s="22"/>
       <c r="B40" s="22" t="s">
         <v>100</v>
@@ -42299,7 +42299,7 @@
       <c r="AQ40" s="49"/>
       <c r="AR40" s="49"/>
     </row>
-    <row r="41" spans="1:44">
+    <row r="41" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A41" s="22"/>
       <c r="B41" s="22" t="s">
         <v>101</v>
@@ -42351,7 +42351,7 @@
       <c r="AQ41" s="49"/>
       <c r="AR41" s="49"/>
     </row>
-    <row r="42" spans="1:44">
+    <row r="42" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A42" s="22"/>
       <c r="B42" s="22" t="s">
         <v>102</v>
@@ -42403,7 +42403,7 @@
       <c r="AQ42" s="49"/>
       <c r="AR42" s="49"/>
     </row>
-    <row r="43" spans="1:44">
+    <row r="43" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A43" s="22"/>
       <c r="B43" s="22" t="s">
         <v>103</v>
@@ -42455,7 +42455,7 @@
       <c r="AQ43" s="49"/>
       <c r="AR43" s="49"/>
     </row>
-    <row r="44" spans="1:44">
+    <row r="44" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A44" s="22"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -42501,7 +42501,7 @@
       <c r="AQ44" s="22"/>
       <c r="AR44" s="22"/>
     </row>
-    <row r="45" spans="1:44">
+    <row r="45" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A45" s="22"/>
       <c r="B45" s="47" t="s">
         <v>104</v>
@@ -42549,7 +42549,7 @@
       <c r="AQ45" s="22"/>
       <c r="AR45" s="22"/>
     </row>
-    <row r="46" spans="1:44">
+    <row r="46" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A46" s="22"/>
       <c r="B46" s="22" t="s">
         <v>101</v>
@@ -42603,7 +42603,7 @@
       <c r="AQ46" s="49"/>
       <c r="AR46" s="49"/>
     </row>
-    <row r="47" spans="1:44">
+    <row r="47" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A47" s="22"/>
       <c r="B47" s="22" t="s">
         <v>102</v>
@@ -42657,7 +42657,7 @@
       <c r="AQ47" s="38"/>
       <c r="AR47" s="38"/>
     </row>
-    <row r="48" spans="1:44">
+    <row r="48" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A48" s="22"/>
       <c r="B48" s="22" t="s">
         <v>103</v>
@@ -42711,7 +42711,7 @@
       <c r="AQ48" s="22"/>
       <c r="AR48" s="22"/>
     </row>
-    <row r="49" spans="1:44">
+    <row r="49" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A49" s="22"/>
       <c r="C49" s="22"/>
       <c r="D49" s="22"/>
@@ -42756,7 +42756,7 @@
       <c r="AQ49" s="22"/>
       <c r="AR49" s="22"/>
     </row>
-    <row r="50" spans="1:44" ht="15.75">
+    <row r="50" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A50" s="22"/>
       <c r="B50" s="23" t="s">
         <v>105</v>
@@ -42804,7 +42804,7 @@
       <c r="AQ50" s="22"/>
       <c r="AR50" s="22"/>
     </row>
-    <row r="51" spans="1:44" ht="15.75">
+    <row r="51" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A51" s="22"/>
       <c r="B51" s="118">
         <v>0.25</v>
@@ -42856,7 +42856,7 @@
       <c r="AQ51" s="22"/>
       <c r="AR51" s="22"/>
     </row>
-    <row r="52" spans="1:44" ht="15.75">
+    <row r="52" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A52" s="22"/>
       <c r="B52" s="118">
         <v>0.5</v>
@@ -42908,7 +42908,7 @@
       <c r="AQ52" s="22"/>
       <c r="AR52" s="22"/>
     </row>
-    <row r="53" spans="1:44" ht="15.75">
+    <row r="53" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A53" s="22"/>
       <c r="B53" s="119">
         <v>0.75</v>
@@ -42960,7 +42960,7 @@
       <c r="AQ53" s="22"/>
       <c r="AR53" s="22"/>
     </row>
-    <row r="54" spans="1:44" ht="15.75">
+    <row r="54" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A54" s="22"/>
       <c r="B54" s="117"/>
       <c r="C54" s="22"/>
@@ -43006,7 +43006,7 @@
       <c r="AQ54" s="22"/>
       <c r="AR54" s="22"/>
     </row>
-    <row r="55" spans="1:44" ht="20.45" thickBot="1">
+    <row r="55" spans="1:44" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="22"/>
       <c r="B55" s="24" t="s">
         <v>106</v>
@@ -43054,7 +43054,7 @@
       <c r="AQ55" s="22"/>
       <c r="AR55" s="22"/>
     </row>
-    <row r="56" spans="1:44" ht="16.149999999999999" thickTop="1">
+    <row r="56" spans="1:44" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A56" s="22"/>
       <c r="B56" s="22"/>
       <c r="C56" s="22"/>
@@ -43100,7 +43100,7 @@
       <c r="AQ56" s="22"/>
       <c r="AR56" s="22"/>
     </row>
-    <row r="57" spans="1:44">
+    <row r="57" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A57" s="22"/>
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
@@ -43147,7 +43147,7 @@
       <c r="AQ57" s="22"/>
       <c r="AR57" s="22"/>
     </row>
-    <row r="58" spans="1:44">
+    <row r="58" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A58" s="22"/>
       <c r="B58" s="22" t="s">
         <v>106</v>
@@ -43198,7 +43198,7 @@
       <c r="AQ58" s="22"/>
       <c r="AR58" s="22"/>
     </row>
-    <row r="59" spans="1:44">
+    <row r="59" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A59" s="22"/>
       <c r="B59" s="22"/>
       <c r="C59" s="22"/>
@@ -43244,7 +43244,7 @@
       <c r="AQ59" s="22"/>
       <c r="AR59" s="22"/>
     </row>
-    <row r="60" spans="1:44">
+    <row r="60" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A60" s="22"/>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -43290,7 +43290,7 @@
       <c r="AQ60" s="22"/>
       <c r="AR60" s="22"/>
     </row>
-    <row r="61" spans="1:44" ht="20.45" thickBot="1">
+    <row r="61" spans="1:44" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="22"/>
       <c r="B61" s="24" t="s">
         <v>108</v>
@@ -43338,7 +43338,7 @@
       <c r="AQ61" s="22"/>
       <c r="AR61" s="22"/>
     </row>
-    <row r="62" spans="1:44" ht="16.149999999999999" thickTop="1">
+    <row r="62" spans="1:44" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A62" s="22"/>
       <c r="B62" s="22"/>
       <c r="C62" s="22">
@@ -43392,7 +43392,7 @@
       <c r="AQ62" s="22"/>
       <c r="AR62" s="22"/>
     </row>
-    <row r="63" spans="1:44">
+    <row r="63" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A63" s="22"/>
       <c r="B63" s="22" t="s">
         <v>109</v>
@@ -43452,7 +43452,7 @@
       <c r="AQ63" s="22"/>
       <c r="AR63" s="22"/>
     </row>
-    <row r="64" spans="1:44">
+    <row r="64" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A64" s="22"/>
       <c r="B64" s="22"/>
       <c r="C64" s="22"/>
@@ -43500,7 +43500,7 @@
       <c r="AQ64" s="22"/>
       <c r="AR64" s="22"/>
     </row>
-    <row r="65" spans="1:44">
+    <row r="65" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A65" s="22"/>
       <c r="B65" s="22"/>
       <c r="C65" s="22"/>
@@ -43546,7 +43546,7 @@
       <c r="AQ65" s="22"/>
       <c r="AR65" s="22"/>
     </row>
-    <row r="66" spans="1:44" ht="20.45" thickBot="1">
+    <row r="66" spans="1:44" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="22"/>
       <c r="B66" s="24" t="s">
         <v>113</v>
@@ -43594,7 +43594,7 @@
       <c r="AQ66" s="22"/>
       <c r="AR66" s="22"/>
     </row>
-    <row r="67" spans="1:44" ht="16.149999999999999" thickTop="1">
+    <row r="67" spans="1:44" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A67" s="22"/>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -43640,7 +43640,7 @@
       <c r="AQ67" s="22"/>
       <c r="AR67" s="22"/>
     </row>
-    <row r="68" spans="1:44" ht="16.149999999999999" thickBot="1">
+    <row r="68" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="61"/>
       <c r="B68" s="62" t="s">
         <v>114</v>
@@ -43690,7 +43690,7 @@
       <c r="AQ68" s="22"/>
       <c r="AR68" s="22"/>
     </row>
-    <row r="69" spans="1:44">
+    <row r="69" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A69" s="61"/>
       <c r="B69" s="22" t="s">
         <v>109</v>
@@ -43745,7 +43745,7 @@
       <c r="AQ69" s="22"/>
       <c r="AR69" s="22"/>
     </row>
-    <row r="70" spans="1:44">
+    <row r="70" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A70" s="61"/>
       <c r="B70" s="22"/>
       <c r="C70" s="22"/>
@@ -43791,7 +43791,7 @@
       <c r="AQ70" s="22"/>
       <c r="AR70" s="22"/>
     </row>
-    <row r="71" spans="1:44">
+    <row r="71" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A71" s="61"/>
       <c r="B71" s="22"/>
       <c r="C71" s="22"/>
@@ -43837,7 +43837,7 @@
       <c r="AQ71" s="22"/>
       <c r="AR71" s="22"/>
     </row>
-    <row r="72" spans="1:44" ht="16.149999999999999" thickBot="1">
+    <row r="72" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A72" s="61"/>
       <c r="B72" s="62" t="s">
         <v>118</v>
@@ -43891,7 +43891,7 @@
       <c r="AQ72" s="22"/>
       <c r="AR72" s="22"/>
     </row>
-    <row r="73" spans="1:44">
+    <row r="73" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A73" s="61"/>
       <c r="B73" s="22" t="s">
         <v>109</v>
@@ -43949,7 +43949,7 @@
       <c r="AQ73" s="22"/>
       <c r="AR73" s="22"/>
     </row>
-    <row r="74" spans="1:44">
+    <row r="74" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A74" s="22"/>
       <c r="B74" s="22" t="s">
         <v>121</v>
@@ -44001,7 +44001,7 @@
       <c r="AQ74" s="22"/>
       <c r="AR74" s="22"/>
     </row>
-    <row r="75" spans="1:44">
+    <row r="75" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A75" s="22"/>
       <c r="B75" s="22" t="s">
         <v>122</v>
@@ -44052,7 +44052,7 @@
       <c r="AQ75" s="22"/>
       <c r="AR75" s="22"/>
     </row>
-    <row r="76" spans="1:44">
+    <row r="76" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A76" s="22"/>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -44098,7 +44098,7 @@
       <c r="AQ76" s="22"/>
       <c r="AR76" s="22"/>
     </row>
-    <row r="77" spans="1:44" ht="16.149999999999999" thickBot="1">
+    <row r="77" spans="1:44" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A77" s="22"/>
       <c r="B77" s="62" t="s">
         <v>123</v>
@@ -44146,7 +44146,7 @@
       <c r="AQ77" s="22"/>
       <c r="AR77" s="22"/>
     </row>
-    <row r="78" spans="1:44">
+    <row r="78" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A78" s="22"/>
       <c r="B78" s="22"/>
       <c r="C78" s="22"/>
@@ -44192,7 +44192,7 @@
       <c r="AQ78" s="22"/>
       <c r="AR78" s="22"/>
     </row>
-    <row r="79" spans="1:44">
+    <row r="79" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A79" s="22"/>
       <c r="B79" s="47" t="s">
         <v>124</v>
@@ -44240,7 +44240,7 @@
       <c r="AQ79" s="22"/>
       <c r="AR79" s="22"/>
     </row>
-    <row r="80" spans="1:44">
+    <row r="80" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A80" s="22"/>
       <c r="B80" s="22"/>
       <c r="C80" s="47"/>
@@ -44298,7 +44298,7 @@
       <c r="AQ80" s="22"/>
       <c r="AR80" s="22"/>
     </row>
-    <row r="81" spans="1:44">
+    <row r="81" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A81" s="22"/>
       <c r="B81" s="47" t="s">
         <v>125</v>
@@ -44358,7 +44358,7 @@
       <c r="AQ81" s="22"/>
       <c r="AR81" s="22"/>
     </row>
-    <row r="82" spans="1:44">
+    <row r="82" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A82" s="22"/>
       <c r="B82" s="47" t="s">
         <v>127</v>
@@ -44416,7 +44416,7 @@
       <c r="AQ82" s="22"/>
       <c r="AR82" s="22"/>
     </row>
-    <row r="83" spans="1:44">
+    <row r="83" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A83" s="22"/>
       <c r="B83" s="47" t="s">
         <v>128</v>
@@ -44474,7 +44474,7 @@
       <c r="AQ83" s="22"/>
       <c r="AR83" s="22"/>
     </row>
-    <row r="84" spans="1:44">
+    <row r="84" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A84" s="22"/>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -44520,7 +44520,7 @@
       <c r="AQ84" s="22"/>
       <c r="AR84" s="22"/>
     </row>
-    <row r="85" spans="1:44">
+    <row r="85" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A85" s="22"/>
       <c r="B85" s="22"/>
       <c r="C85" s="22"/>
@@ -44570,7 +44570,7 @@
       <c r="AQ85" s="22"/>
       <c r="AR85" s="22"/>
     </row>
-    <row r="86" spans="1:44">
+    <row r="86" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A86" s="22"/>
       <c r="B86" s="47" t="s">
         <v>128</v>
@@ -44623,7 +44623,7 @@
       <c r="AQ86" s="22"/>
       <c r="AR86" s="22"/>
     </row>
-    <row r="87" spans="1:44">
+    <row r="87" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A87" s="22"/>
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
@@ -44671,7 +44671,7 @@
       <c r="AQ87" s="22"/>
       <c r="AR87" s="22"/>
     </row>
-    <row r="88" spans="1:44">
+    <row r="88" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A88" s="22"/>
       <c r="B88" s="47" t="s">
         <v>129</v>
@@ -44721,7 +44721,7 @@
       <c r="AQ88" s="22"/>
       <c r="AR88" s="22"/>
     </row>
-    <row r="89" spans="1:44">
+    <row r="89" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A89" s="22"/>
       <c r="B89" s="22"/>
       <c r="C89" s="22"/>
@@ -44825,7 +44825,7 @@
       <c r="AQ89" s="22"/>
       <c r="AR89" s="22"/>
     </row>
-    <row r="90" spans="1:44">
+    <row r="90" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A90" s="22"/>
       <c r="B90" s="47" t="s">
         <v>131</v>
@@ -44931,7 +44931,7 @@
       <c r="AQ90" s="22"/>
       <c r="AR90" s="22"/>
     </row>
-    <row r="91" spans="1:44">
+    <row r="91" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A91" s="22"/>
       <c r="B91" s="47" t="s">
         <v>132</v>
@@ -45037,7 +45037,7 @@
       <c r="AQ91" s="22"/>
       <c r="AR91" s="22"/>
     </row>
-    <row r="92" spans="1:44">
+    <row r="92" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A92" s="22"/>
       <c r="B92" s="47" t="s">
         <v>133</v>
@@ -45143,7 +45143,7 @@
       <c r="AQ92" s="22"/>
       <c r="AR92" s="22"/>
     </row>
-    <row r="93" spans="1:44">
+    <row r="93" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A93" s="22"/>
       <c r="B93" s="22"/>
       <c r="C93" s="22"/>
@@ -45189,7 +45189,7 @@
       <c r="AQ93" s="22"/>
       <c r="AR93" s="22"/>
     </row>
-    <row r="94" spans="1:44">
+    <row r="94" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A94" s="22"/>
       <c r="B94" s="47" t="s">
         <v>134</v>
@@ -45324,7 +45324,7 @@
       <c r="AQ94" s="22"/>
       <c r="AR94" s="22"/>
     </row>
-    <row r="95" spans="1:44">
+    <row r="95" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A95" s="22"/>
       <c r="B95" s="47" t="s">
         <v>135</v>
@@ -45459,7 +45459,7 @@
       <c r="AQ95" s="22"/>
       <c r="AR95" s="22"/>
     </row>
-    <row r="96" spans="1:44">
+    <row r="96" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A96" s="22"/>
       <c r="B96" s="47" t="s">
         <v>136</v>
@@ -45594,7 +45594,7 @@
       <c r="AQ96" s="22"/>
       <c r="AR96" s="22"/>
     </row>
-    <row r="97" spans="1:44">
+    <row r="97" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A97" s="22"/>
       <c r="B97" s="22"/>
       <c r="C97" s="22"/>
@@ -45640,7 +45640,7 @@
       <c r="AQ97" s="22"/>
       <c r="AR97" s="22"/>
     </row>
-    <row r="98" spans="1:44">
+    <row r="98" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A98" s="22"/>
       <c r="B98" s="22"/>
       <c r="C98" s="22"/>
@@ -45686,7 +45686,7 @@
       <c r="AQ98" s="22"/>
       <c r="AR98" s="22"/>
     </row>
-    <row r="99" spans="1:44">
+    <row r="99" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A99" s="22"/>
       <c r="B99" s="22"/>
       <c r="C99" s="22"/>
@@ -45732,7 +45732,7 @@
       <c r="AQ99" s="22"/>
       <c r="AR99" s="22"/>
     </row>
-    <row r="100" spans="1:44">
+    <row r="100" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A100" s="22"/>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -45778,7 +45778,7 @@
       <c r="AQ100" s="22"/>
       <c r="AR100" s="22"/>
     </row>
-    <row r="101" spans="1:44">
+    <row r="101" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A101" s="22"/>
       <c r="B101" s="47" t="s">
         <v>137</v>
@@ -45826,7 +45826,7 @@
       <c r="AQ101" s="22"/>
       <c r="AR101" s="22"/>
     </row>
-    <row r="102" spans="1:44">
+    <row r="102" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A102" s="22"/>
       <c r="C102" s="22"/>
       <c r="D102" s="47">
@@ -45875,7 +45875,7 @@
       <c r="AQ102" s="22"/>
       <c r="AR102" s="22"/>
     </row>
-    <row r="103" spans="1:44">
+    <row r="103" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A103" s="22"/>
       <c r="B103" s="47" t="s">
         <v>138</v>
@@ -45929,7 +45929,7 @@
       <c r="AQ103" s="22"/>
       <c r="AR103" s="22"/>
     </row>
-    <row r="104" spans="1:44">
+    <row r="104" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A104" s="22"/>
       <c r="B104" s="47" t="s">
         <v>139</v>
@@ -45983,7 +45983,7 @@
       <c r="AQ104" s="22"/>
       <c r="AR104" s="22"/>
     </row>
-    <row r="105" spans="1:44">
+    <row r="105" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A105" s="22"/>
       <c r="B105" s="47" t="s">
         <v>140</v>
@@ -46037,7 +46037,7 @@
       <c r="AQ105" s="22"/>
       <c r="AR105" s="22"/>
     </row>
-    <row r="106" spans="1:44">
+    <row r="106" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A106" s="22"/>
       <c r="B106" s="47" t="s">
         <v>141</v>
@@ -46091,7 +46091,7 @@
       <c r="AQ106" s="22"/>
       <c r="AR106" s="22"/>
     </row>
-    <row r="107" spans="1:44">
+    <row r="107" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A107" s="22"/>
       <c r="B107" s="22"/>
       <c r="C107" s="22"/>
@@ -46137,7 +46137,7 @@
       <c r="AQ107" s="22"/>
       <c r="AR107" s="22"/>
     </row>
-    <row r="108" spans="1:44" ht="20.45" thickBot="1">
+    <row r="108" spans="1:44" ht="21" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A108" s="22"/>
       <c r="B108" s="24" t="s">
         <v>142</v>
@@ -46185,7 +46185,7 @@
       <c r="AQ108" s="22"/>
       <c r="AR108" s="22"/>
     </row>
-    <row r="109" spans="1:44" ht="16.149999999999999" thickTop="1">
+    <row r="109" spans="1:44" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A109" s="22"/>
       <c r="B109" s="22"/>
       <c r="C109" s="22"/>
@@ -46231,7 +46231,7 @@
       <c r="AQ109" s="22"/>
       <c r="AR109" s="22"/>
     </row>
-    <row r="110" spans="1:44">
+    <row r="110" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A110" s="22"/>
       <c r="B110" s="22" t="s">
         <v>143</v>
@@ -46285,7 +46285,7 @@
       <c r="AQ110" s="22"/>
       <c r="AR110" s="22"/>
     </row>
-    <row r="111" spans="1:44">
+    <row r="111" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A111" s="22"/>
       <c r="B111" s="22" t="s">
         <v>145</v>
@@ -46339,7 +46339,7 @@
       <c r="AQ111" s="22"/>
       <c r="AR111" s="22"/>
     </row>
-    <row r="112" spans="1:44">
+    <row r="112" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A112" s="22"/>
       <c r="F112" s="22"/>
       <c r="G112" s="22"/>
@@ -46381,7 +46381,7 @@
       <c r="AQ112" s="22"/>
       <c r="AR112" s="22"/>
     </row>
-    <row r="113" spans="1:44">
+    <row r="113" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A113" s="22"/>
       <c r="B113" s="22"/>
       <c r="C113" s="22"/>
@@ -46427,7 +46427,7 @@
       <c r="AQ113" s="22"/>
       <c r="AR113" s="22"/>
     </row>
-    <row r="114" spans="1:44">
+    <row r="114" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A114" s="22"/>
       <c r="B114" s="22"/>
       <c r="C114" s="22"/>
@@ -46473,7 +46473,7 @@
       <c r="AQ114" s="22"/>
       <c r="AR114" s="22"/>
     </row>
-    <row r="115" spans="1:44">
+    <row r="115" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A115" s="22"/>
       <c r="B115" s="22"/>
       <c r="C115" s="22"/>
@@ -46533,20 +46533,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D6861D5-92D2-D641-8B69-D340B89E733B}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="125" t="s">
         <v>146</v>
       </c>
       <c r="B1" s="125"/>
       <c r="C1" s="125"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>147</v>
       </c>
@@ -46554,7 +46554,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>406</v>
       </c>
@@ -46562,7 +46562,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>358</v>
       </c>
@@ -46570,7 +46570,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>149</v>
       </c>
@@ -46582,13 +46582,13 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="125" t="s">
         <v>151</v>
       </c>
       <c r="B9" s="125"/>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>2024</v>
       </c>
@@ -46596,7 +46596,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>152</v>
       </c>
@@ -46610,7 +46610,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>153</v>
       </c>
@@ -46621,13 +46621,13 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="125" t="s">
         <v>154</v>
       </c>
       <c r="B14" s="125"/>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B15">
         <v>2024</v>
       </c>
@@ -46635,7 +46635,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>152</v>
       </c>
@@ -46646,7 +46646,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>153</v>
       </c>
@@ -46674,13 +46674,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{29B5CED7-41F6-FF44-BBF4-DBE0D457C1E0}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="A2:C7"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="68.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -46691,7 +46691,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>156</v>
       </c>
@@ -46702,7 +46702,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>159</v>
       </c>
@@ -46713,7 +46713,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>161</v>
       </c>
@@ -46724,7 +46724,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>164</v>
       </c>
@@ -46735,7 +46735,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>167</v>
       </c>
@@ -46755,34 +46755,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E9E050F-07F8-FE48-85C0-51954A76FC24}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="A1:AH30"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.25" customWidth="1"/>
+    <col min="1" max="1" width="23.1640625" customWidth="1"/>
     <col min="2" max="2" width="12.5" customWidth="1"/>
     <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="20.25" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="20.1640625" customWidth="1"/>
     <col min="17" max="17" width="17.5" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="17.5" customWidth="1"/>
     <col min="19" max="19" width="29" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.1640625" bestFit="1" customWidth="1"/>
     <col min="21" max="22" width="14" customWidth="1"/>
-    <col min="23" max="23" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="15.25" customWidth="1"/>
-    <col min="27" max="27" width="29.75" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.25" customWidth="1"/>
+    <col min="23" max="23" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="15.1640625" customWidth="1"/>
+    <col min="27" max="27" width="29.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.1640625" customWidth="1"/>
     <col min="29" max="29" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="20.25" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="55.25" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="55.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.2">
       <c r="I1" t="s">
         <v>170</v>
       </c>
@@ -46790,7 +46790,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="2" spans="1:34">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -46894,7 +46894,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="3" spans="1:34">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>202</v>
       </c>
@@ -46995,7 +46995,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="4" spans="1:34">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>223</v>
       </c>
@@ -47087,7 +47087,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:34">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>237</v>
       </c>
@@ -47175,7 +47175,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="6" spans="1:34">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>250</v>
       </c>
@@ -47262,7 +47262,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="7" spans="1:34">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>261</v>
       </c>
@@ -47360,7 +47360,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="8" spans="1:34">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>269</v>
       </c>
@@ -47452,7 +47452,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="9" spans="1:34">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>281</v>
       </c>
@@ -47548,7 +47548,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" spans="1:34">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>261</v>
       </c>
@@ -47638,7 +47638,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="11" spans="1:34">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>292</v>
       </c>
@@ -47735,7 +47735,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="12" spans="1:34">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>237</v>
       </c>
@@ -47826,7 +47826,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="13" spans="1:34">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>305</v>
       </c>
@@ -47921,7 +47921,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="14" spans="1:34">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>309</v>
       </c>
@@ -48014,7 +48014,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="15" spans="1:34">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>315</v>
       </c>
@@ -48095,7 +48095,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="16" spans="1:34">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>323</v>
       </c>
@@ -48170,7 +48170,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="17" spans="1:34">
+    <row r="17" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>326</v>
       </c>
@@ -48235,7 +48235,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="18" spans="1:34" ht="19.899999999999999" customHeight="1">
+    <row r="18" spans="1:34" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>332</v>
       </c>
@@ -48317,7 +48317,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="19" spans="1:34">
+    <row r="19" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>339</v>
       </c>
@@ -48395,7 +48395,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="20" spans="1:34">
+    <row r="20" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>343</v>
       </c>
@@ -48431,7 +48431,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="21" spans="1:34">
+    <row r="21" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>345</v>
       </c>
@@ -48474,7 +48474,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="22" spans="1:34">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>348</v>
       </c>
@@ -48516,32 +48516,32 @@
         <v>350</v>
       </c>
     </row>
-    <row r="23" spans="1:34">
+    <row r="23" spans="1:34" x14ac:dyDescent="0.2">
       <c r="M23" s="12"/>
       <c r="Z23" s="5">
         <f>AVERAGE(Z3:Z22)</f>
         <v>4.185833333333334</v>
       </c>
     </row>
-    <row r="24" spans="1:34">
+    <row r="24" spans="1:34" x14ac:dyDescent="0.2">
       <c r="M24" s="12"/>
     </row>
-    <row r="25" spans="1:34">
+    <row r="25" spans="1:34" x14ac:dyDescent="0.2">
       <c r="M25" s="12"/>
     </row>
-    <row r="26" spans="1:34">
+    <row r="26" spans="1:34" x14ac:dyDescent="0.2">
       <c r="M26" s="12"/>
     </row>
-    <row r="27" spans="1:34">
+    <row r="27" spans="1:34" x14ac:dyDescent="0.2">
       <c r="M27" s="12"/>
     </row>
-    <row r="28" spans="1:34">
+    <row r="28" spans="1:34" x14ac:dyDescent="0.2">
       <c r="M28" s="12"/>
     </row>
-    <row r="29" spans="1:34">
+    <row r="29" spans="1:34" x14ac:dyDescent="0.2">
       <c r="M29" s="12"/>
     </row>
-    <row r="30" spans="1:34">
+    <row r="30" spans="1:34" x14ac:dyDescent="0.2">
       <c r="M30" s="12"/>
     </row>
   </sheetData>
@@ -48578,20 +48578,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E6A38EC-CB22-4C8C-9093-9377000E9A23}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:T50"/>
-  <sheetFormatPr defaultColWidth="11.25" defaultRowHeight="15.6"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.25" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.1640625" customWidth="1"/>
     <col min="3" max="3" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="19" width="18.25" customWidth="1"/>
+    <col min="11" max="11" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="19" width="18.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>4</v>
       </c>
@@ -48650,7 +48650,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="2" spans="1:20" hidden="1">
+    <row r="2" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>309</v>
       </c>
@@ -48705,7 +48705,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="3" spans="1:20" hidden="1">
+    <row r="3" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>369</v>
       </c>
@@ -48772,7 +48772,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="4" spans="1:20" hidden="1">
+    <row r="4" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>326</v>
       </c>
@@ -48802,7 +48802,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:20" hidden="1">
+    <row r="5" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>323</v>
       </c>
@@ -48864,7 +48864,7 @@
       </c>
       <c r="S5" s="13"/>
     </row>
-    <row r="6" spans="1:20" hidden="1">
+    <row r="6" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>261</v>
       </c>
@@ -48919,7 +48919,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="7" spans="1:20" hidden="1">
+    <row r="7" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>261</v>
       </c>
@@ -48971,7 +48971,7 @@
         <v>58035000</v>
       </c>
     </row>
-    <row r="8" spans="1:20" hidden="1">
+    <row r="8" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>261</v>
       </c>
@@ -49038,7 +49038,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="9" spans="1:20" hidden="1">
+    <row r="9" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>339</v>
       </c>
@@ -49102,7 +49102,7 @@
         <v>39140033.75</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>339</v>
       </c>
@@ -49172,7 +49172,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="11" spans="1:20" hidden="1">
+    <row r="11" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>380</v>
       </c>
@@ -49220,7 +49220,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="12" spans="1:20" hidden="1">
+    <row r="12" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>380</v>
       </c>
@@ -49284,7 +49284,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="13" spans="1:20" hidden="1">
+    <row r="13" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>380</v>
       </c>
@@ -49332,7 +49332,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="14" spans="1:20" hidden="1">
+    <row r="14" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>380</v>
       </c>
@@ -49380,7 +49380,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="15" spans="1:20" hidden="1">
+    <row r="15" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>380</v>
       </c>
@@ -49428,7 +49428,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="16" spans="1:20">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>380</v>
       </c>
@@ -49495,7 +49495,7 @@
         <v>87000000</v>
       </c>
     </row>
-    <row r="17" spans="1:20">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>380</v>
       </c>
@@ -49546,7 +49546,7 @@
         <v>35000000</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>380</v>
       </c>
@@ -49597,7 +49597,7 @@
         <v>48000000</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>380</v>
       </c>
@@ -49648,7 +49648,7 @@
         <v>69000000</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>380</v>
       </c>
@@ -49699,7 +49699,7 @@
         <v>68000000</v>
       </c>
     </row>
-    <row r="21" spans="1:20" hidden="1">
+    <row r="21" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>237</v>
       </c>
@@ -49751,7 +49751,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>237</v>
       </c>
@@ -49807,7 +49807,7 @@
       </c>
       <c r="T22" s="20"/>
     </row>
-    <row r="23" spans="1:20" hidden="1">
+    <row r="23" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>223</v>
       </c>
@@ -49859,7 +49859,7 @@
         <v>3650000</v>
       </c>
     </row>
-    <row r="24" spans="1:20" hidden="1">
+    <row r="24" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>281</v>
       </c>
@@ -49926,7 +49926,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="25" spans="1:20">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>281</v>
       </c>
@@ -49993,7 +49993,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="26" spans="1:20">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>281</v>
       </c>
@@ -50048,7 +50048,7 @@
         <v>31354838</v>
       </c>
     </row>
-    <row r="27" spans="1:20" hidden="1">
+    <row r="27" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>348</v>
       </c>
@@ -50097,7 +50097,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="16.899999999999999" hidden="1" customHeight="1">
+    <row r="28" spans="1:20" ht="17" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>348</v>
       </c>
@@ -50149,7 +50149,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="16.899999999999999" customHeight="1">
+    <row r="29" spans="1:20" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>348</v>
       </c>
@@ -50201,7 +50201,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="30" spans="1:20">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>348</v>
       </c>
@@ -50265,7 +50265,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="31" spans="1:20">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>348</v>
       </c>
@@ -50317,7 +50317,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="32" spans="1:20" hidden="1">
+    <row r="32" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>348</v>
       </c>
@@ -50378,7 +50378,7 @@
         <v>157410000</v>
       </c>
     </row>
-    <row r="33" spans="1:20" hidden="1">
+    <row r="33" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>305</v>
       </c>
@@ -50445,7 +50445,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="34" spans="1:20" hidden="1">
+    <row r="34" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>292</v>
       </c>
@@ -50512,7 +50512,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="35" spans="1:20" hidden="1">
+    <row r="35" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>332</v>
       </c>
@@ -50579,7 +50579,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="36" spans="1:20" hidden="1">
+    <row r="36" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>332</v>
       </c>
@@ -50643,7 +50643,7 @@
         <v>1250000000</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>250</v>
       </c>
@@ -50710,7 +50710,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>250</v>
       </c>
@@ -50765,7 +50765,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>250</v>
       </c>
@@ -50820,7 +50820,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="40" spans="1:20" hidden="1">
+    <row r="40" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>250</v>
       </c>
@@ -50872,7 +50872,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="41" spans="1:20" hidden="1">
+    <row r="41" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>250</v>
       </c>
@@ -50939,7 +50939,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="42" spans="1:20" hidden="1">
+    <row r="42" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>250</v>
       </c>
@@ -50991,7 +50991,7 @@
         <v>1000000</v>
       </c>
     </row>
-    <row r="43" spans="1:20">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>202</v>
       </c>
@@ -51058,7 +51058,7 @@
         <v>2110761</v>
       </c>
     </row>
-    <row r="44" spans="1:20" hidden="1">
+    <row r="44" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>202</v>
       </c>
@@ -51125,7 +51125,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="45" spans="1:20" hidden="1">
+    <row r="45" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>315</v>
       </c>
@@ -51177,7 +51177,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>315</v>
       </c>
@@ -51232,7 +51232,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="47" spans="1:20" hidden="1">
+    <row r="47" spans="1:20" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>269</v>
       </c>
@@ -51278,13 +51278,13 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.2">
       <c r="I48" s="75"/>
       <c r="J48" s="75"/>
       <c r="K48" s="75"/>
       <c r="L48" s="75"/>
     </row>
-    <row r="50" spans="9:12">
+    <row r="50" spans="9:12" x14ac:dyDescent="0.2">
       <c r="I50" s="75"/>
       <c r="J50" s="75"/>
       <c r="L50" s="75"/>
@@ -51334,5 +51334,9 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80800E50-85F1-8745-9372-153DAD5875F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80800E50-85F1-8745-9372-153DAD5875F5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/DataMashup"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>